--- a/لیست_قیمت_سوکت عباسی.xlsx
+++ b/لیست_قیمت_سوکت عباسی.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yaser\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BFA989A-6F82-4479-885F-D9CCA51B818A}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9DDDFF8-0C33-49AD-9718-F321A88A37E3}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="9525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2290" uniqueCount="1456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2294" uniqueCount="1459">
   <si>
     <t>کد کالا</t>
   </si>
@@ -3371,54 +3371,9 @@
     <t>1307000</t>
   </si>
   <si>
-    <t>503000</t>
-  </si>
-  <si>
-    <t>1672000</t>
-  </si>
-  <si>
     <t>0</t>
   </si>
   <si>
-    <t>1086000</t>
-  </si>
-  <si>
-    <t>4064000</t>
-  </si>
-  <si>
-    <t>2710000</t>
-  </si>
-  <si>
-    <t>1521000</t>
-  </si>
-  <si>
-    <t>4180000</t>
-  </si>
-  <si>
-    <t>616000</t>
-  </si>
-  <si>
-    <t>1923000</t>
-  </si>
-  <si>
-    <t>952000</t>
-  </si>
-  <si>
-    <t>30088000</t>
-  </si>
-  <si>
-    <t>1506000</t>
-  </si>
-  <si>
-    <t>5016000</t>
-  </si>
-  <si>
-    <t>3330000</t>
-  </si>
-  <si>
-    <t>1873000</t>
-  </si>
-  <si>
     <t>سیم خودرویی - دارای استاندارد ایزو9001 - سر سوکت پلی آمید نسوز - سر سیم دوخار کاپ دار</t>
   </si>
   <si>
@@ -3530,868 +3485,922 @@
     <t>کد 433 دسته سیم دینام انژکتور نیسان</t>
   </si>
   <si>
-    <t>9194000</t>
-  </si>
-  <si>
-    <t>1060000</t>
-  </si>
-  <si>
-    <t>1438000</t>
-  </si>
-  <si>
-    <t>1169000</t>
-  </si>
-  <si>
-    <t>1710000</t>
-  </si>
-  <si>
-    <t>1114000</t>
-  </si>
-  <si>
-    <t>629000</t>
-  </si>
-  <si>
     <t>554000</t>
   </si>
   <si>
-    <t>787000</t>
-  </si>
-  <si>
-    <t>1131000</t>
-  </si>
-  <si>
-    <t>855000</t>
-  </si>
-  <si>
-    <t>1172000</t>
-  </si>
-  <si>
-    <t>1140000</t>
-  </si>
-  <si>
-    <t>1591000</t>
-  </si>
-  <si>
-    <t>2226000</t>
-  </si>
-  <si>
     <t>1840000</t>
   </si>
   <si>
-    <t>926000</t>
-  </si>
-  <si>
-    <t>1789000</t>
-  </si>
-  <si>
-    <t>2305000</t>
-  </si>
-  <si>
-    <t>2605000</t>
-  </si>
-  <si>
-    <t>3035000</t>
-  </si>
-  <si>
-    <t>601000</t>
-  </si>
-  <si>
-    <t>466000</t>
-  </si>
-  <si>
-    <t>735000</t>
-  </si>
-  <si>
-    <t>979000</t>
-  </si>
-  <si>
-    <t>1142000</t>
-  </si>
-  <si>
-    <t>1955000</t>
-  </si>
-  <si>
-    <t>1465000</t>
-  </si>
-  <si>
-    <t>1572000</t>
-  </si>
-  <si>
-    <t>2251000</t>
-  </si>
-  <si>
-    <t>2440000</t>
-  </si>
-  <si>
-    <t>2225000</t>
-  </si>
-  <si>
-    <t>355000</t>
-  </si>
-  <si>
-    <t>544000</t>
-  </si>
-  <si>
-    <t>1737000</t>
-  </si>
-  <si>
-    <t>2170000</t>
-  </si>
-  <si>
-    <t>1304000</t>
-  </si>
-  <si>
-    <t>1763000</t>
-  </si>
-  <si>
-    <t>3579000</t>
-  </si>
-  <si>
-    <t>4147000</t>
-  </si>
-  <si>
-    <t>382000</t>
-  </si>
-  <si>
-    <t>435000</t>
-  </si>
-  <si>
     <t>1195000</t>
   </si>
   <si>
-    <t>2792000</t>
-  </si>
-  <si>
-    <t>3513000</t>
-  </si>
-  <si>
-    <t>3780000</t>
-  </si>
-  <si>
-    <t>3118000</t>
-  </si>
-  <si>
-    <t>2468000</t>
-  </si>
-  <si>
-    <t>1603000</t>
-  </si>
-  <si>
-    <t>626000</t>
-  </si>
-  <si>
-    <t>1033000</t>
-  </si>
-  <si>
-    <t>869000</t>
-  </si>
-  <si>
-    <t>1221000</t>
-  </si>
-  <si>
-    <t>1628000</t>
-  </si>
-  <si>
-    <t>517000</t>
-  </si>
-  <si>
-    <t>1656000</t>
-  </si>
-  <si>
-    <t>2332000</t>
-  </si>
-  <si>
-    <t>2089000</t>
-  </si>
-  <si>
-    <t>1251000</t>
-  </si>
-  <si>
-    <t>2767000</t>
-  </si>
-  <si>
-    <t>4201000</t>
-  </si>
-  <si>
     <t>4471000</t>
   </si>
   <si>
-    <t>844000</t>
-  </si>
-  <si>
-    <t>1385000</t>
-  </si>
-  <si>
-    <t>1846000</t>
-  </si>
-  <si>
-    <t>2657000</t>
-  </si>
-  <si>
     <t>2981000</t>
   </si>
   <si>
-    <t>6771000</t>
-  </si>
-  <si>
-    <t>3929000</t>
-  </si>
-  <si>
-    <t>1004000</t>
-  </si>
-  <si>
-    <t>1278000</t>
-  </si>
-  <si>
-    <t>2523000</t>
-  </si>
-  <si>
-    <t>4827000</t>
-  </si>
-  <si>
-    <t>3678000</t>
-  </si>
-  <si>
-    <t>6811000</t>
-  </si>
-  <si>
-    <t>817000</t>
-  </si>
-  <si>
-    <t>5001000</t>
-  </si>
-  <si>
-    <t>670000</t>
-  </si>
-  <si>
-    <t>2738000</t>
-  </si>
-  <si>
-    <t>3604000</t>
-  </si>
-  <si>
-    <t>2926000</t>
-  </si>
-  <si>
-    <t>2426000</t>
-  </si>
-  <si>
-    <t>1707000</t>
-  </si>
-  <si>
-    <t>2677000</t>
-  </si>
-  <si>
     <t>1674000</t>
   </si>
   <si>
-    <t>538000</t>
-  </si>
-  <si>
-    <t>387000</t>
-  </si>
-  <si>
-    <t>1494000</t>
-  </si>
-  <si>
-    <t>1356000</t>
-  </si>
-  <si>
-    <t>761000</t>
-  </si>
-  <si>
-    <t>1980000</t>
-  </si>
-  <si>
-    <t>491000</t>
-  </si>
-  <si>
-    <t>13540000</t>
-  </si>
-  <si>
-    <t>5092000</t>
-  </si>
-  <si>
-    <t>4875000</t>
-  </si>
-  <si>
-    <t>139000</t>
-  </si>
-  <si>
-    <t>193000</t>
-  </si>
-  <si>
-    <t>2063000</t>
-  </si>
-  <si>
-    <t>3525000</t>
-  </si>
-  <si>
-    <t>3090000</t>
-  </si>
-  <si>
-    <t>2032000</t>
-  </si>
-  <si>
-    <t>835000</t>
-  </si>
-  <si>
-    <t>1757000</t>
-  </si>
-  <si>
-    <t>44295000</t>
-  </si>
-  <si>
-    <t>3712000</t>
-  </si>
-  <si>
-    <t>3822000</t>
-  </si>
-  <si>
-    <t>2843000</t>
-  </si>
-  <si>
-    <t>2007000</t>
-  </si>
-  <si>
-    <t>4849000</t>
-  </si>
-  <si>
-    <t>2275000</t>
-  </si>
-  <si>
-    <t>9831000</t>
-  </si>
-  <si>
-    <t>20895000</t>
-  </si>
-  <si>
-    <t>2384000</t>
-  </si>
-  <si>
-    <t>409000</t>
-  </si>
-  <si>
-    <t>786000</t>
-  </si>
-  <si>
-    <t>3629000</t>
-  </si>
-  <si>
-    <t>6521000</t>
-  </si>
-  <si>
-    <t>274000</t>
-  </si>
-  <si>
-    <t>520000</t>
-  </si>
-  <si>
-    <t>336000</t>
-  </si>
-  <si>
-    <t>3428000</t>
-  </si>
-  <si>
-    <t>2411000</t>
-  </si>
-  <si>
-    <t>3846000</t>
-  </si>
-  <si>
-    <t>4173000</t>
-  </si>
-  <si>
-    <t>1029000</t>
-  </si>
-  <si>
-    <t>1329000</t>
-  </si>
-  <si>
-    <t>3009000</t>
-  </si>
-  <si>
-    <t>1598000</t>
-  </si>
-  <si>
-    <t>2160000</t>
-  </si>
-  <si>
-    <t>31500000</t>
-  </si>
-  <si>
-    <t>5443000</t>
-  </si>
-  <si>
-    <t>4356000</t>
-  </si>
-  <si>
-    <t>3520000</t>
-  </si>
-  <si>
     <t>4598000</t>
   </si>
   <si>
-    <t>4014000</t>
-  </si>
-  <si>
-    <t>1815000</t>
-  </si>
-  <si>
-    <t>3880000</t>
-  </si>
-  <si>
-    <t>5450000</t>
-  </si>
-  <si>
-    <t>3000000</t>
-  </si>
-  <si>
-    <t>4200000</t>
-  </si>
-  <si>
     <t>678000</t>
   </si>
   <si>
-    <t>2576000</t>
-  </si>
-  <si>
-    <t>1021000</t>
-  </si>
-  <si>
     <t>2116000</t>
   </si>
   <si>
-    <t>3897000</t>
-  </si>
-  <si>
-    <t>3227000</t>
-  </si>
-  <si>
-    <t>4198000</t>
-  </si>
-  <si>
-    <t>6554000</t>
-  </si>
-  <si>
-    <t>1573000</t>
-  </si>
-  <si>
     <t>1048000</t>
   </si>
   <si>
-    <t>462000</t>
-  </si>
-  <si>
-    <t>3335000</t>
-  </si>
-  <si>
-    <t>2198000</t>
-  </si>
-  <si>
-    <t>4579000</t>
-  </si>
-  <si>
-    <t>3170000</t>
-  </si>
-  <si>
-    <t>5148000</t>
-  </si>
-  <si>
-    <t>19550000</t>
-  </si>
-  <si>
-    <t>11700000</t>
-  </si>
-  <si>
-    <t>12950000</t>
-  </si>
-  <si>
-    <t>10500000</t>
-  </si>
-  <si>
-    <t>3010000</t>
-  </si>
-  <si>
-    <t>5256000</t>
-  </si>
-  <si>
-    <t>13040000</t>
-  </si>
-  <si>
-    <t>8527000</t>
-  </si>
-  <si>
-    <t>2626000</t>
-  </si>
-  <si>
-    <t>8026000</t>
-  </si>
-  <si>
-    <t>6605000</t>
-  </si>
-  <si>
-    <t>8293000</t>
-  </si>
-  <si>
-    <t>1952000</t>
-  </si>
-  <si>
-    <t>5636000</t>
-  </si>
-  <si>
-    <t>1249000</t>
-  </si>
-  <si>
-    <t>21481000</t>
-  </si>
-  <si>
-    <t>27415000</t>
-  </si>
-  <si>
-    <t>4750000</t>
-  </si>
-  <si>
-    <t>6650000</t>
-  </si>
-  <si>
-    <t>575000</t>
-  </si>
-  <si>
-    <t>2358000</t>
-  </si>
-  <si>
-    <t>2876000</t>
-  </si>
-  <si>
-    <t>8100000</t>
-  </si>
-  <si>
-    <t>9990000</t>
-  </si>
-  <si>
-    <t>24130000</t>
-  </si>
-  <si>
-    <t>14050000</t>
-  </si>
-  <si>
-    <t>17350000</t>
-  </si>
-  <si>
-    <t>12300000</t>
-  </si>
-  <si>
-    <t>25900000</t>
-  </si>
-  <si>
-    <t>10290000</t>
-  </si>
-  <si>
-    <t>4113000</t>
-  </si>
-  <si>
-    <t>6890000</t>
-  </si>
-  <si>
-    <t>2952000</t>
-  </si>
-  <si>
-    <t>2142000</t>
-  </si>
-  <si>
-    <t>6687000</t>
-  </si>
-  <si>
-    <t>896000</t>
-  </si>
-  <si>
-    <t>3387000</t>
-  </si>
-  <si>
-    <t>1005000</t>
-  </si>
-  <si>
-    <t>4516000</t>
-  </si>
-  <si>
-    <t>6020000</t>
-  </si>
-  <si>
-    <t>16048000</t>
-  </si>
-  <si>
-    <t>2493000</t>
-  </si>
-  <si>
-    <t>1491000</t>
-  </si>
-  <si>
-    <t>653000</t>
-  </si>
-  <si>
-    <t>4255000</t>
-  </si>
-  <si>
-    <t>3064000</t>
-  </si>
-  <si>
-    <t>3596000</t>
-  </si>
-  <si>
-    <t>1223000</t>
-  </si>
-  <si>
     <t>1657000</t>
   </si>
   <si>
-    <t>33431000</t>
-  </si>
-  <si>
-    <t>16383000</t>
-  </si>
-  <si>
-    <t>14043000</t>
-  </si>
-  <si>
-    <t>2632000</t>
-  </si>
-  <si>
-    <t>8946000</t>
-  </si>
-  <si>
-    <t>13207000</t>
-  </si>
-  <si>
-    <t>2342000</t>
-  </si>
-  <si>
-    <t>7273000</t>
-  </si>
-  <si>
-    <t>1898000</t>
-  </si>
-  <si>
-    <t>2955000</t>
-  </si>
-  <si>
-    <t>710000</t>
-  </si>
-  <si>
-    <t>13358000</t>
-  </si>
-  <si>
-    <t>7023000</t>
-  </si>
-  <si>
-    <t>32428000</t>
-  </si>
-  <si>
-    <t>1547000</t>
-  </si>
-  <si>
-    <t>7691000</t>
-  </si>
-  <si>
-    <t>6437000</t>
-  </si>
-  <si>
     <t>5518000</t>
   </si>
   <si>
-    <t>436000</t>
-  </si>
-  <si>
-    <t>2549000</t>
-  </si>
-  <si>
-    <t>9613000</t>
-  </si>
-  <si>
-    <t>7774000</t>
-  </si>
-  <si>
-    <t>5384000</t>
-  </si>
-  <si>
-    <t>15547000</t>
-  </si>
-  <si>
-    <t>1473000</t>
-  </si>
-  <si>
-    <t>7749000</t>
-  </si>
-  <si>
-    <t>3794000</t>
-  </si>
-  <si>
     <t>3663000</t>
   </si>
   <si>
-    <t>5476000</t>
-  </si>
-  <si>
-    <t>3443000</t>
-  </si>
-  <si>
-    <t>7607000</t>
-  </si>
-  <si>
-    <t>4365000</t>
-  </si>
-  <si>
-    <t>3985000</t>
-  </si>
-  <si>
-    <t>2593000</t>
-  </si>
-  <si>
-    <t>3095000</t>
-  </si>
-  <si>
-    <t>3930000</t>
-  </si>
-  <si>
-    <t>4549000</t>
-  </si>
-  <si>
-    <t>6905000</t>
-  </si>
-  <si>
-    <t>3262000</t>
-  </si>
-  <si>
-    <t>4565000</t>
-  </si>
-  <si>
-    <t>10167000</t>
-  </si>
-  <si>
-    <t>3011000</t>
-  </si>
-  <si>
-    <t>2042000</t>
-  </si>
-  <si>
-    <t>3145000</t>
-  </si>
-  <si>
     <t>2819000</t>
   </si>
   <si>
-    <t>5218000</t>
-  </si>
-  <si>
-    <t>1523000</t>
-  </si>
-  <si>
-    <t>4381000</t>
-  </si>
-  <si>
-    <t>24739000</t>
-  </si>
-  <si>
-    <t>2259000</t>
-  </si>
-  <si>
-    <t>3278000</t>
-  </si>
-  <si>
-    <t>2996000</t>
-  </si>
-  <si>
-    <t>2644000</t>
-  </si>
-  <si>
-    <t>5921000</t>
-  </si>
-  <si>
-    <t>6405000</t>
-  </si>
-  <si>
-    <t>10266000</t>
-  </si>
-  <si>
-    <t>9211000</t>
-  </si>
-  <si>
-    <t>14056000</t>
-  </si>
-  <si>
-    <t>2331000</t>
-  </si>
-  <si>
-    <t>2414000</t>
-  </si>
-  <si>
-    <t>5337000</t>
-  </si>
-  <si>
-    <t>4389000</t>
-  </si>
-  <si>
-    <t>2766000</t>
-  </si>
-  <si>
-    <t>10021000</t>
-  </si>
-  <si>
-    <t>2601000</t>
-  </si>
-  <si>
-    <t>5850000</t>
-  </si>
-  <si>
-    <t>3061000</t>
-  </si>
-  <si>
-    <t>5283000</t>
-  </si>
-  <si>
     <t>2061000</t>
   </si>
   <si>
-    <t>1328000</t>
-  </si>
-  <si>
-    <t>920000</t>
-  </si>
-  <si>
-    <t>671000</t>
-  </si>
-  <si>
-    <t>14127000</t>
-  </si>
-  <si>
-    <t>11620000</t>
-  </si>
-  <si>
-    <t>16634000</t>
-  </si>
-  <si>
-    <t>3129000</t>
-  </si>
-  <si>
-    <t>8694000</t>
-  </si>
-  <si>
-    <t>10281000</t>
-  </si>
-  <si>
-    <t>13291000</t>
-  </si>
-  <si>
     <t>10114000</t>
   </si>
   <si>
-    <t>8192000</t>
-  </si>
-  <si>
-    <t>15212000</t>
-  </si>
-  <si>
-    <t>8276000</t>
+    <t>4231000</t>
+  </si>
+  <si>
+    <t>1077000</t>
+  </si>
+  <si>
+    <t>513000</t>
+  </si>
+  <si>
+    <t>809000</t>
+  </si>
+  <si>
+    <t>662000</t>
+  </si>
+  <si>
+    <t>1582000</t>
+  </si>
+  <si>
+    <t>2151000</t>
+  </si>
+  <si>
+    <t>1461000</t>
+  </si>
+  <si>
+    <t>1019000</t>
+  </si>
+  <si>
+    <t>1257000</t>
+  </si>
+  <si>
+    <t>956000</t>
+  </si>
+  <si>
+    <t>1137000</t>
+  </si>
+  <si>
+    <t>689000</t>
+  </si>
+  <si>
+    <t>599000</t>
+  </si>
+  <si>
+    <t>479000</t>
+  </si>
+  <si>
+    <t>421000</t>
+  </si>
+  <si>
+    <t>2477000</t>
+  </si>
+  <si>
+    <t>1878000</t>
+  </si>
+  <si>
+    <t>2669000</t>
+  </si>
+  <si>
+    <t>3219000</t>
+  </si>
+  <si>
+    <t>1791000</t>
+  </si>
+  <si>
+    <t>1166000</t>
+  </si>
+  <si>
+    <t>1344000</t>
+  </si>
+  <si>
+    <t>1254000</t>
+  </si>
+  <si>
+    <t>1751000</t>
+  </si>
+  <si>
+    <t>2449000</t>
+  </si>
+  <si>
+    <t>391000</t>
+  </si>
+  <si>
+    <t>1842000</t>
+  </si>
+  <si>
+    <t>1105000</t>
+  </si>
+  <si>
+    <t>2270000</t>
+  </si>
+  <si>
+    <t>302000</t>
+  </si>
+  <si>
+    <t>1286000</t>
+  </si>
+  <si>
+    <t>899000</t>
+  </si>
+  <si>
+    <t>3339000</t>
+  </si>
+  <si>
+    <t>2866000</t>
+  </si>
+  <si>
+    <t>941000</t>
+  </si>
+  <si>
+    <t>866000</t>
+  </si>
+  <si>
+    <t>1290000</t>
+  </si>
+  <si>
+    <t>1911000</t>
+  </si>
+  <si>
+    <t>2804000</t>
+  </si>
+  <si>
+    <t>541000</t>
+  </si>
+  <si>
+    <t>838000</t>
+  </si>
+  <si>
+    <t>592000</t>
+  </si>
+  <si>
+    <t>1968000</t>
+  </si>
+  <si>
+    <t>865000</t>
+  </si>
+  <si>
+    <t>450000</t>
+  </si>
+  <si>
+    <t>1524000</t>
+  </si>
+  <si>
+    <t>1730000</t>
+  </si>
+  <si>
+    <t>1315000</t>
+  </si>
+  <si>
+    <t>4562000</t>
+  </si>
+  <si>
+    <t>3937000</t>
+  </si>
+  <si>
+    <t>7356000</t>
+  </si>
+  <si>
+    <t>2743000</t>
+  </si>
+  <si>
+    <t>1823000</t>
+  </si>
+  <si>
+    <t>8001000</t>
+  </si>
+  <si>
+    <t>480000</t>
+  </si>
+  <si>
+    <t>4174000</t>
+  </si>
+  <si>
+    <t>2024000</t>
+  </si>
+  <si>
+    <t>5004000</t>
+  </si>
+  <si>
+    <t>2684000</t>
+  </si>
+  <si>
+    <t>153000</t>
+  </si>
+  <si>
+    <t>213000</t>
+  </si>
+  <si>
+    <t>692000</t>
+  </si>
+  <si>
+    <t>610000</t>
+  </si>
+  <si>
+    <t>1245000</t>
+  </si>
+  <si>
+    <t>7596000</t>
+  </si>
+  <si>
+    <t>4820000</t>
+  </si>
+  <si>
+    <t>986000</t>
+  </si>
+  <si>
+    <t>30157000</t>
+  </si>
+  <si>
+    <t>426000</t>
+  </si>
+  <si>
+    <t>1644000</t>
+  </si>
+  <si>
+    <t>1612000</t>
+  </si>
+  <si>
+    <t>1492000</t>
+  </si>
+  <si>
+    <t>27213000</t>
+  </si>
+  <si>
+    <t>2376000</t>
+  </si>
+  <si>
+    <t>1758000</t>
+  </si>
+  <si>
+    <t>2536000</t>
+  </si>
+  <si>
+    <t>919000</t>
+  </si>
+  <si>
+    <t>1940000</t>
+  </si>
+  <si>
+    <t>1764000</t>
+  </si>
+  <si>
+    <t>7493000</t>
+  </si>
+  <si>
+    <t>4046000</t>
+  </si>
+  <si>
+    <t>5310000</t>
+  </si>
+  <si>
+    <t>3430000</t>
+  </si>
+  <si>
+    <t>7726000</t>
+  </si>
+  <si>
+    <t>5740000</t>
+  </si>
+  <si>
+    <t>1822000</t>
+  </si>
+  <si>
+    <t>737000</t>
+  </si>
+  <si>
+    <t>2387000</t>
+  </si>
+  <si>
+    <t>14694000</t>
+  </si>
+  <si>
+    <t>4084000</t>
+  </si>
+  <si>
+    <t>1435000</t>
+  </si>
+  <si>
+    <t>3865000</t>
+  </si>
+  <si>
+    <t>4323000</t>
+  </si>
+  <si>
+    <t>2853000</t>
+  </si>
+  <si>
+    <t>3405000</t>
+  </si>
+  <si>
+    <t>1621000</t>
+  </si>
+  <si>
+    <t>1012000</t>
+  </si>
+  <si>
+    <t>1226000</t>
+  </si>
+  <si>
+    <t>569000</t>
+  </si>
+  <si>
+    <t>1406000</t>
+  </si>
+  <si>
+    <t>2031000</t>
+  </si>
+  <si>
+    <t>929000</t>
+  </si>
+  <si>
+    <t>4158000</t>
+  </si>
+  <si>
+    <t>370000</t>
+  </si>
+  <si>
+    <t>3965000</t>
+  </si>
+  <si>
+    <t>3012000</t>
+  </si>
+  <si>
+    <t>1462000</t>
+  </si>
+  <si>
+    <t>2566000</t>
+  </si>
+  <si>
+    <t>1377000</t>
+  </si>
+  <si>
+    <t>3044000</t>
+  </si>
+  <si>
+    <t>3072000</t>
+  </si>
+  <si>
+    <t>1124000</t>
+  </si>
+  <si>
+    <t>572000</t>
+  </si>
+  <si>
+    <t>1153000</t>
+  </si>
+  <si>
+    <t>1132000</t>
+  </si>
+  <si>
+    <t>4622000</t>
+  </si>
+  <si>
+    <t>2715000</t>
+  </si>
+  <si>
+    <t>509000</t>
+  </si>
+  <si>
+    <t>5602000</t>
+  </si>
+  <si>
+    <t>5363000</t>
+  </si>
+  <si>
+    <t>4416000</t>
+  </si>
+  <si>
+    <t>746000</t>
+  </si>
+  <si>
+    <t>2945000</t>
+  </si>
+  <si>
+    <t>7449000</t>
+  </si>
+  <si>
+    <t>2448000</t>
+  </si>
+  <si>
+    <t>1933000</t>
+  </si>
+  <si>
+    <t>7210000</t>
+  </si>
+  <si>
+    <t>2328000</t>
+  </si>
+  <si>
+    <t>14894000</t>
+  </si>
+  <si>
+    <t>4919000</t>
+  </si>
+  <si>
+    <t>2298000</t>
+  </si>
+  <si>
+    <t>3878000</t>
+  </si>
+  <si>
+    <t>2208000</t>
+  </si>
+  <si>
+    <t>4591000</t>
+  </si>
+  <si>
+    <t>2623000</t>
+  </si>
+  <si>
+    <t>4322000</t>
+  </si>
+  <si>
+    <t>9123000</t>
+  </si>
+  <si>
+    <t>2834000</t>
+  </si>
+  <si>
+    <t>2236000</t>
+  </si>
+  <si>
+    <t>5502000</t>
+  </si>
+  <si>
+    <t>5334000</t>
+  </si>
+  <si>
+    <t>2357000</t>
+  </si>
+  <si>
+    <t>5037000</t>
+  </si>
+  <si>
+    <t>2776000</t>
+  </si>
+  <si>
+    <t>3280000</t>
+  </si>
+  <si>
+    <t>2923000</t>
+  </si>
+  <si>
+    <t>3310000</t>
+  </si>
+  <si>
+    <t>4618000</t>
+  </si>
+  <si>
+    <t>3550000</t>
+  </si>
+  <si>
+    <t>3128000</t>
+  </si>
+  <si>
+    <t>4205000</t>
+  </si>
+  <si>
+    <t>1106000</t>
+  </si>
+  <si>
+    <t>3399000</t>
+  </si>
+  <si>
+    <t>2653000</t>
+  </si>
+  <si>
+    <t>2178000</t>
+  </si>
+  <si>
+    <t>2418000</t>
+  </si>
+  <si>
+    <t>3487000</t>
+  </si>
+  <si>
+    <t>3992000</t>
+  </si>
+  <si>
+    <t>719000</t>
+  </si>
+  <si>
+    <t>1997000</t>
+  </si>
+  <si>
+    <t>1641000</t>
+  </si>
+  <si>
+    <t>2148000</t>
+  </si>
+  <si>
+    <t>1881000</t>
+  </si>
+  <si>
+    <t>2503000</t>
+  </si>
+  <si>
+    <t>1374000</t>
+  </si>
+  <si>
+    <t>3669000</t>
+  </si>
+  <si>
+    <t>5663000</t>
+  </si>
+  <si>
+    <t>5058000</t>
+  </si>
+  <si>
+    <t>8829000</t>
+  </si>
+  <si>
+    <t>633000</t>
+  </si>
+  <si>
+    <t>10815000</t>
+  </si>
+  <si>
+    <t>7266000</t>
+  </si>
+  <si>
+    <t>6622000</t>
+  </si>
+  <si>
+    <t>4681000</t>
+  </si>
+  <si>
+    <t>3872000</t>
+  </si>
+  <si>
+    <t>4792000</t>
+  </si>
+  <si>
+    <t>6200000</t>
+  </si>
+  <si>
+    <t>4287000</t>
+  </si>
+  <si>
+    <t>3726000</t>
+  </si>
+  <si>
+    <t>2889000</t>
+  </si>
+  <si>
+    <t>23630000</t>
+  </si>
+  <si>
+    <t>4968000</t>
+  </si>
+  <si>
+    <t>1731000</t>
+  </si>
+  <si>
+    <t>3164000</t>
+  </si>
+  <si>
+    <t>5988000</t>
+  </si>
+  <si>
+    <t>3248000</t>
+  </si>
+  <si>
+    <t>1346000</t>
+  </si>
+  <si>
+    <t>22985000</t>
+  </si>
+  <si>
+    <t>2594000</t>
+  </si>
+  <si>
+    <t>48725000</t>
+  </si>
+  <si>
+    <t>3371000</t>
+  </si>
+  <si>
+    <t>17653000</t>
+  </si>
+  <si>
+    <t>5782000</t>
+  </si>
+  <si>
+    <t>7579000</t>
+  </si>
+  <si>
+    <t>4525000</t>
+  </si>
+  <si>
+    <t>3311000</t>
+  </si>
+  <si>
+    <t>3251000</t>
+  </si>
+  <si>
+    <t>14344000</t>
+  </si>
+  <si>
+    <t>1702000</t>
+  </si>
+  <si>
+    <t>3956000</t>
+  </si>
+  <si>
+    <t>9380000</t>
+  </si>
+  <si>
+    <t>9841000</t>
+  </si>
+  <si>
+    <t>781000</t>
+  </si>
+  <si>
+    <t>14528000</t>
+  </si>
+  <si>
+    <t>2088000</t>
+  </si>
+  <si>
+    <t>8461000</t>
+  </si>
+  <si>
+    <t>8524000</t>
+  </si>
+  <si>
+    <t>6070000</t>
+  </si>
+  <si>
+    <t>7081000</t>
+  </si>
+  <si>
+    <t>2577000</t>
+  </si>
+  <si>
+    <t>17102000</t>
+  </si>
+  <si>
+    <t>5923000</t>
+  </si>
+  <si>
+    <t>35671000</t>
+  </si>
+  <si>
+    <t>10575000</t>
+  </si>
+  <si>
+    <t>8552000</t>
+  </si>
+  <si>
+    <t>36775000</t>
+  </si>
+  <si>
+    <t>33097000</t>
+  </si>
+  <si>
+    <t>2896000</t>
+  </si>
+  <si>
+    <t>4030000</t>
+  </si>
+  <si>
+    <t>3788000</t>
+  </si>
+  <si>
+    <t>4384000</t>
+  </si>
+  <si>
+    <t>6024000</t>
+  </si>
+  <si>
+    <t>8368000</t>
+  </si>
+  <si>
+    <t>4802000</t>
+  </si>
+  <si>
+    <t>3589000</t>
+  </si>
+  <si>
+    <t>5022000</t>
+  </si>
+  <si>
+    <t>11184000</t>
+  </si>
+  <si>
+    <t>3313000</t>
+  </si>
+  <si>
+    <t>2247000</t>
+  </si>
+  <si>
+    <t>3460000</t>
+  </si>
+  <si>
+    <t>3101000</t>
+  </si>
+  <si>
+    <t>1676000</t>
+  </si>
+  <si>
+    <t>2485000</t>
+  </si>
+  <si>
+    <t>3606000</t>
+  </si>
+  <si>
+    <t>3296000</t>
+  </si>
+  <si>
+    <t>2909000</t>
+  </si>
+  <si>
+    <t>6514000</t>
+  </si>
+  <si>
+    <t>7046000</t>
+  </si>
+  <si>
+    <t>11293000</t>
+  </si>
+  <si>
+    <t>10133000</t>
+  </si>
+  <si>
+    <t>15462000</t>
+  </si>
+  <si>
+    <t>2565000</t>
+  </si>
+  <si>
+    <t>2656000</t>
+  </si>
+  <si>
+    <t>5871000</t>
+  </si>
+  <si>
+    <t>4828000</t>
+  </si>
+  <si>
+    <t>3043000</t>
+  </si>
+  <si>
+    <t>11024000</t>
+  </si>
+  <si>
+    <t>2862000</t>
+  </si>
+  <si>
+    <t>6435000</t>
+  </si>
+  <si>
+    <t>3368000</t>
+  </si>
+  <si>
+    <t>5812000</t>
+  </si>
+  <si>
+    <t>2268000</t>
+  </si>
+  <si>
+    <t>739000</t>
+  </si>
+  <si>
+    <t>9000900</t>
+  </si>
+  <si>
+    <t>کد 9000900 چراغ سقفی led تیبا</t>
+  </si>
+  <si>
+    <t>3771000</t>
+  </si>
+  <si>
+    <t>7174000</t>
+  </si>
+  <si>
+    <t>4268000</t>
+  </si>
+  <si>
+    <t>5995000</t>
+  </si>
+  <si>
+    <t>21505000</t>
+  </si>
+  <si>
+    <t>12870000</t>
+  </si>
+  <si>
+    <t>14245000</t>
+  </si>
+  <si>
+    <t>11550000</t>
+  </si>
+  <si>
+    <t>34650000</t>
+  </si>
+  <si>
+    <t>7315000</t>
+  </si>
+  <si>
+    <t>5225000</t>
+  </si>
+  <si>
+    <t>28490000</t>
+  </si>
+  <si>
+    <t>15448000</t>
+  </si>
+  <si>
+    <t>18022000</t>
+  </si>
+  <si>
+    <t>11319000</t>
+  </si>
+  <si>
+    <t>3300000</t>
+  </si>
+  <si>
+    <t>4620000</t>
+  </si>
+  <si>
+    <t>8910000</t>
+  </si>
+  <si>
+    <t>10989000</t>
+  </si>
+  <si>
+    <t>13530000</t>
+  </si>
+  <si>
+    <t>15455000</t>
+  </si>
+  <si>
+    <t>19085000</t>
+  </si>
+  <si>
+    <t>26543000</t>
+  </si>
+  <si>
+    <t>15540000</t>
+  </si>
+  <si>
+    <t>12782000</t>
+  </si>
+  <si>
+    <t>18298000</t>
+  </si>
+  <si>
+    <t>3442000</t>
+  </si>
+  <si>
+    <t>9564000</t>
+  </si>
+  <si>
+    <t>11310000</t>
+  </si>
+  <si>
+    <t>14621000</t>
+  </si>
+  <si>
+    <t>11126000</t>
+  </si>
+  <si>
+    <t>9012000</t>
+  </si>
+  <si>
+    <t>16734000</t>
+  </si>
+  <si>
+    <t>9104000</t>
   </si>
 </sst>
 </file>
@@ -4814,10 +4823,10 @@
         <v>562</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1169</v>
+        <v>1190</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -4831,7 +4840,7 @@
         <v>1114</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -4842,10 +4851,10 @@
         <v>564</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -4856,10 +4865,10 @@
         <v>565</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1171</v>
+        <v>1200</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -4870,10 +4879,10 @@
         <v>566</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1172</v>
+        <v>1332</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -4884,10 +4893,10 @@
         <v>567</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1172</v>
+        <v>1332</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -4898,10 +4907,10 @@
         <v>568</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1173</v>
+        <v>1267</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -4912,10 +4921,10 @@
         <v>569</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1174</v>
+        <v>1231</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -4926,10 +4935,10 @@
         <v>570</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1174</v>
+        <v>1231</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -4940,10 +4949,10 @@
         <v>571</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>1175</v>
+        <v>1232</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -4954,10 +4963,10 @@
         <v>572</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>1175</v>
+        <v>1232</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -4968,10 +4977,10 @@
         <v>573</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>1176</v>
+        <v>1205</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -4982,10 +4991,10 @@
         <v>574</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>1176</v>
+        <v>1205</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -4996,10 +5005,10 @@
         <v>575</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>1177</v>
+        <v>1233</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -5010,10 +5019,10 @@
         <v>576</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>1177</v>
+        <v>1233</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -5024,10 +5033,10 @@
         <v>577</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>1178</v>
+        <v>1204</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -5038,10 +5047,10 @@
         <v>578</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>1178</v>
+        <v>1204</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -5052,10 +5061,10 @@
         <v>579</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>1176</v>
+        <v>1205</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -5066,10 +5075,10 @@
         <v>580</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>1176</v>
+        <v>1205</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -5080,10 +5089,10 @@
         <v>581</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>1179</v>
+        <v>1206</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -5094,10 +5103,10 @@
         <v>582</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>1179</v>
+        <v>1206</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -5108,10 +5117,10 @@
         <v>583</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>1116</v>
+        <v>1154</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -5122,10 +5131,10 @@
         <v>584</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>1116</v>
+        <v>1154</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -5136,10 +5145,10 @@
         <v>585</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>1180</v>
+        <v>1192</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -5150,10 +5159,10 @@
         <v>586</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>1180</v>
+        <v>1192</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -5164,10 +5173,10 @@
         <v>587</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>1181</v>
+        <v>1193</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -5178,10 +5187,10 @@
         <v>588</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>1181</v>
+        <v>1193</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -5192,10 +5201,10 @@
         <v>589</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>1182</v>
+        <v>1194</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -5206,10 +5215,10 @@
         <v>590</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>1182</v>
+        <v>1194</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -5220,10 +5229,10 @@
         <v>591</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>1183</v>
+        <v>1226</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -5234,10 +5243,10 @@
         <v>592</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>1183</v>
+        <v>1226</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -5248,10 +5257,10 @@
         <v>593</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>1184</v>
+        <v>1177</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -5262,10 +5271,10 @@
         <v>594</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>1185</v>
+        <v>1212</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -5276,10 +5285,10 @@
         <v>595</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>1186</v>
+        <v>1245</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -5290,10 +5299,10 @@
         <v>596</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>1187</v>
+        <v>1203</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -5304,10 +5313,10 @@
         <v>597</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -5318,10 +5327,10 @@
         <v>598</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>1188</v>
+        <v>1202</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -5332,10 +5341,10 @@
         <v>599</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>1189</v>
+        <v>1173</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -5346,10 +5355,10 @@
         <v>600</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>1190</v>
+        <v>1171</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -5360,10 +5369,10 @@
         <v>601</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>1191</v>
+        <v>1172</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -5374,10 +5383,10 @@
         <v>602</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>1192</v>
+        <v>1170</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -5388,10 +5397,10 @@
         <v>603</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>1193</v>
+        <v>1178</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -5402,10 +5411,10 @@
         <v>604</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>1184</v>
+        <v>1177</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -5416,10 +5425,10 @@
         <v>605</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -5430,10 +5439,10 @@
         <v>606</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>1194</v>
+        <v>1175</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -5444,10 +5453,10 @@
         <v>607</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>1195</v>
+        <v>1240</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -5458,10 +5467,10 @@
         <v>608</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>1193</v>
+        <v>1178</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -5472,10 +5481,10 @@
         <v>609</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>1196</v>
+        <v>1216</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -5486,10 +5495,10 @@
         <v>610</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>1171</v>
+        <v>1200</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -5500,10 +5509,10 @@
         <v>611</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>1197</v>
+        <v>1185</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -5514,10 +5523,10 @@
         <v>612</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>1130</v>
+        <v>1167</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -5528,10 +5537,10 @@
         <v>613</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>1198</v>
+        <v>1228</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -5542,10 +5551,10 @@
         <v>614</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>1199</v>
+        <v>1294</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -5556,10 +5565,10 @@
         <v>615</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>1200</v>
+        <v>1195</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -5570,10 +5579,10 @@
         <v>616</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>1201</v>
+        <v>1182</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -5584,10 +5593,10 @@
         <v>617</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>1202</v>
+        <v>1207</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -5598,10 +5607,10 @@
         <v>618</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>1203</v>
+        <v>1257</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -5612,10 +5621,10 @@
         <v>619</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>1120</v>
+        <v>1157</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -5626,10 +5635,10 @@
         <v>620</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>1204</v>
+        <v>1260</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -5640,10 +5649,10 @@
         <v>621</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>1205</v>
+        <v>1247</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -5654,10 +5663,10 @@
         <v>622</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>1188</v>
+        <v>1202</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -5668,10 +5677,10 @@
         <v>623</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>1206</v>
+        <v>1219</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -5682,10 +5691,10 @@
         <v>624</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>1207</v>
+        <v>1218</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -5696,10 +5705,10 @@
         <v>625</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -5710,10 +5719,10 @@
         <v>626</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>1209</v>
+        <v>1183</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -5724,10 +5733,10 @@
         <v>627</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>1201</v>
+        <v>1182</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -5738,10 +5747,10 @@
         <v>628</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -5752,10 +5761,10 @@
         <v>629</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -5766,10 +5775,10 @@
         <v>630</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -5780,10 +5789,10 @@
         <v>631</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>1196</v>
+        <v>1216</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -5794,10 +5803,10 @@
         <v>632</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>1196</v>
+        <v>1216</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -5808,10 +5817,10 @@
         <v>633</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>1196</v>
+        <v>1216</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -5822,10 +5831,10 @@
         <v>634</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>1211</v>
+        <v>1280</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -5836,10 +5845,10 @@
         <v>635</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>1211</v>
+        <v>1280</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -5850,10 +5859,10 @@
         <v>636</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>1212</v>
+        <v>1261</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -5864,10 +5873,10 @@
         <v>637</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>1213</v>
+        <v>1272</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -5878,10 +5887,10 @@
         <v>638</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>1196</v>
+        <v>1216</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -5892,10 +5901,10 @@
         <v>639</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>1196</v>
+        <v>1216</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -5906,10 +5915,10 @@
         <v>640</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>1199</v>
+        <v>1294</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -5920,10 +5929,10 @@
         <v>641</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>1214</v>
+        <v>1252</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -5934,10 +5943,10 @@
         <v>642</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>1215</v>
+        <v>1286</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -5948,10 +5957,10 @@
         <v>643</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>1216</v>
+        <v>1248</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -5962,10 +5971,10 @@
         <v>644</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>1216</v>
+        <v>1248</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -5976,10 +5985,10 @@
         <v>645</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>1191</v>
+        <v>1172</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -5990,10 +5999,10 @@
         <v>646</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>1217</v>
+        <v>1181</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -6004,10 +6013,10 @@
         <v>647</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>1125</v>
+        <v>1162</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -6018,10 +6027,10 @@
         <v>648</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>1218</v>
+        <v>1180</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -6032,10 +6041,10 @@
         <v>649</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>1219</v>
+        <v>1179</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -6046,10 +6055,10 @@
         <v>650</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -6060,10 +6069,10 @@
         <v>651</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>1220</v>
+        <v>1191</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -6074,10 +6083,10 @@
         <v>652</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>1169</v>
+        <v>1190</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -6088,10 +6097,10 @@
         <v>653</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>1221</v>
+        <v>1189</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -6102,10 +6111,10 @@
         <v>654</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>1125</v>
+        <v>1162</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -6116,10 +6125,10 @@
         <v>655</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>1222</v>
+        <v>1268</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -6130,10 +6139,10 @@
         <v>656</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>1217</v>
+        <v>1181</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -6144,10 +6153,10 @@
         <v>657</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>1217</v>
+        <v>1181</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -6158,10 +6167,10 @@
         <v>658</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>1169</v>
+        <v>1190</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -6172,10 +6181,10 @@
         <v>659</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>1169</v>
+        <v>1190</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -6186,10 +6195,10 @@
         <v>660</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>1221</v>
+        <v>1189</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -6200,10 +6209,10 @@
         <v>661</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>1223</v>
+        <v>1255</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -6214,10 +6223,10 @@
         <v>662</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>1223</v>
+        <v>1255</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -6228,10 +6237,10 @@
         <v>663</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>1205</v>
+        <v>1247</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -6242,10 +6251,10 @@
         <v>664</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>1205</v>
+        <v>1247</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
@@ -6256,10 +6265,10 @@
         <v>665</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>1224</v>
+        <v>1277</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -6270,10 +6279,10 @@
         <v>666</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -6284,10 +6293,10 @@
         <v>667</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>1185</v>
+        <v>1212</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -6298,10 +6307,10 @@
         <v>668</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>1225</v>
+        <v>1300</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
@@ -6312,10 +6321,10 @@
         <v>669</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>1226</v>
+        <v>1278</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
@@ -6326,10 +6335,10 @@
         <v>670</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>1227</v>
+        <v>1279</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
@@ -6340,10 +6349,10 @@
         <v>671</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>1187</v>
+        <v>1203</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
@@ -6354,10 +6363,10 @@
         <v>672</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>1228</v>
+        <v>1285</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
@@ -6368,10 +6377,10 @@
         <v>673</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>1229</v>
+        <v>1299</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
@@ -6382,10 +6391,10 @@
         <v>674</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>1186</v>
+        <v>1245</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
@@ -6396,10 +6405,10 @@
         <v>675</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>1230</v>
+        <v>1271</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
@@ -6410,10 +6419,10 @@
         <v>676</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>1230</v>
+        <v>1271</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
@@ -6424,10 +6433,10 @@
         <v>677</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>1221</v>
+        <v>1189</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
@@ -6438,10 +6447,10 @@
         <v>678</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>1231</v>
+        <v>1215</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
@@ -6452,10 +6461,10 @@
         <v>679</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>1232</v>
+        <v>1270</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
@@ -6466,10 +6475,10 @@
         <v>680</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>1233</v>
+        <v>1315</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
@@ -6480,10 +6489,10 @@
         <v>681</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>1234</v>
+        <v>1314</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
@@ -6494,10 +6503,10 @@
         <v>682</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>1125</v>
+        <v>1162</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
@@ -6508,10 +6517,10 @@
         <v>683</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>1118</v>
+        <v>1155</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
@@ -6522,10 +6531,10 @@
         <v>684</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>1121</v>
+        <v>1158</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
@@ -6536,10 +6545,10 @@
         <v>685</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>1235</v>
+        <v>1293</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
@@ -6550,10 +6559,10 @@
         <v>686</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>1235</v>
+        <v>1293</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
@@ -6564,10 +6573,10 @@
         <v>687</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>1235</v>
+        <v>1293</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
@@ -6578,10 +6587,10 @@
         <v>688</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>1236</v>
+        <v>1305</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
@@ -6592,10 +6601,10 @@
         <v>689</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>1118</v>
+        <v>1155</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
@@ -6606,10 +6615,10 @@
         <v>690</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>1118</v>
+        <v>1155</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
@@ -6620,10 +6629,10 @@
         <v>691</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>1237</v>
+        <v>1197</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
@@ -6634,10 +6643,10 @@
         <v>692</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>1237</v>
+        <v>1197</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
@@ -6648,10 +6657,10 @@
         <v>693</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>1238</v>
+        <v>1269</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
@@ -6662,10 +6671,10 @@
         <v>694</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>1239</v>
+        <v>1313</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
@@ -6676,10 +6685,10 @@
         <v>695</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>1238</v>
+        <v>1269</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
@@ -6690,10 +6699,10 @@
         <v>696</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>1185</v>
+        <v>1212</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
@@ -6704,10 +6713,10 @@
         <v>697</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>1240</v>
+        <v>1251</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
@@ -6718,10 +6727,10 @@
         <v>698</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>1241</v>
+        <v>1250</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
@@ -6732,10 +6741,10 @@
         <v>699</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>1242</v>
+        <v>1249</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
@@ -6746,10 +6755,10 @@
         <v>700</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>1243</v>
+        <v>1201</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
@@ -6760,10 +6769,10 @@
         <v>701</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>1243</v>
+        <v>1201</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
@@ -6774,10 +6783,10 @@
         <v>702</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>1244</v>
+        <v>1309</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
@@ -6788,10 +6797,10 @@
         <v>703</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>1123</v>
+        <v>1160</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
@@ -6802,10 +6811,10 @@
         <v>704</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>1123</v>
+        <v>1160</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
@@ -6816,10 +6825,10 @@
         <v>705</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>1123</v>
+        <v>1160</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
@@ -6830,10 +6839,10 @@
         <v>706</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>1123</v>
+        <v>1160</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
@@ -6844,10 +6853,10 @@
         <v>707</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>1245</v>
+        <v>1256</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
@@ -6858,10 +6867,10 @@
         <v>708</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>1245</v>
+        <v>1256</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
@@ -6872,10 +6881,10 @@
         <v>709</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>1245</v>
+        <v>1256</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
@@ -6886,10 +6895,10 @@
         <v>710</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>1245</v>
+        <v>1256</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
@@ -6900,10 +6909,10 @@
         <v>711</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>1246</v>
+        <v>1275</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
@@ -6914,10 +6923,10 @@
         <v>712</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>1247</v>
+        <v>1274</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
@@ -6928,10 +6937,10 @@
         <v>713</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>1248</v>
+        <v>1188</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
@@ -6942,10 +6951,10 @@
         <v>714</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>1249</v>
+        <v>1187</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
@@ -6956,10 +6965,10 @@
         <v>715</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>1250</v>
+        <v>1186</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
@@ -6970,10 +6979,10 @@
         <v>716</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>1220</v>
+        <v>1191</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
@@ -6984,10 +6993,10 @@
         <v>717</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>1124</v>
+        <v>1161</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
@@ -6998,10 +7007,10 @@
         <v>718</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>1203</v>
+        <v>1257</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
@@ -7012,10 +7021,10 @@
         <v>719</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>1251</v>
+        <v>1292</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
@@ -7026,10 +7035,10 @@
         <v>720</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>1252</v>
+        <v>1196</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
@@ -7040,10 +7049,10 @@
         <v>721</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>1253</v>
+        <v>1211</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
@@ -7054,10 +7063,10 @@
         <v>722</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>1254</v>
+        <v>1238</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
@@ -7068,10 +7077,10 @@
         <v>723</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>1254</v>
+        <v>1238</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
@@ -7082,10 +7091,10 @@
         <v>724</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>1255</v>
+        <v>1239</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
@@ -7096,10 +7105,10 @@
         <v>725</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>1256</v>
+        <v>1241</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
@@ -7110,10 +7119,10 @@
         <v>726</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>1220</v>
+        <v>1191</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
@@ -7124,10 +7133,10 @@
         <v>727</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>1221</v>
+        <v>1189</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
@@ -7138,10 +7147,10 @@
         <v>728</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>1189</v>
+        <v>1173</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
@@ -7152,10 +7161,10 @@
         <v>729</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>1243</v>
+        <v>1201</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
@@ -7166,10 +7175,10 @@
         <v>730</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>1171</v>
+        <v>1200</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
@@ -7180,10 +7189,10 @@
         <v>731</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>1257</v>
+        <v>1210</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
@@ -7194,10 +7203,10 @@
         <v>732</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>1176</v>
+        <v>1205</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
@@ -7208,10 +7217,10 @@
         <v>733</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
@@ -7222,10 +7231,10 @@
         <v>734</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>1171</v>
+        <v>1200</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
@@ -7236,10 +7245,10 @@
         <v>735</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>1231</v>
+        <v>1215</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
@@ -7250,10 +7259,10 @@
         <v>736</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>1216</v>
+        <v>1248</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
@@ -7264,10 +7273,10 @@
         <v>737</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>1258</v>
+        <v>1324</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
@@ -7278,10 +7287,10 @@
         <v>738</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>1226</v>
+        <v>1278</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
@@ -7292,10 +7301,10 @@
         <v>739</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>1232</v>
+        <v>1270</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
@@ -7306,66 +7315,66 @@
         <v>740</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>1259</v>
+        <v>1209</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
-        <v>1134</v>
+        <v>1119</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>1152</v>
+        <v>1137</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>1140</v>
+        <v>1125</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>1158</v>
+        <v>1143</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>1451</v>
+        <v>1454</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
-        <v>1138</v>
+        <v>1123</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>1156</v>
+        <v>1141</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>1450</v>
+        <v>1453</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>1137</v>
+        <v>1122</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>1155</v>
+        <v>1140</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>1449</v>
+        <v>1452</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
@@ -7376,10 +7385,10 @@
         <v>741</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>1260</v>
+        <v>1298</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
@@ -7390,10 +7399,10 @@
         <v>742</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>1261</v>
+        <v>1288</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
@@ -7404,10 +7413,10 @@
         <v>743</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>1262</v>
+        <v>1289</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
@@ -7418,10 +7427,10 @@
         <v>744</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>1263</v>
+        <v>1229</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
@@ -7432,10 +7441,10 @@
         <v>745</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>1264</v>
+        <v>1230</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
@@ -7446,10 +7455,10 @@
         <v>746</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>1265</v>
+        <v>1198</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
@@ -7460,10 +7469,10 @@
         <v>747</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>1265</v>
+        <v>1198</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
@@ -7474,10 +7483,10 @@
         <v>748</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>1266</v>
+        <v>1301</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
@@ -7488,10 +7497,10 @@
         <v>749</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>1238</v>
+        <v>1269</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
@@ -7502,10 +7511,10 @@
         <v>750</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>1267</v>
+        <v>1322</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
@@ -7516,10 +7525,10 @@
         <v>751</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>1233</v>
+        <v>1315</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
@@ -7530,10 +7539,10 @@
         <v>752</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>1268</v>
+        <v>1308</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
@@ -7544,10 +7553,10 @@
         <v>753</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>1255</v>
+        <v>1239</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
@@ -7558,10 +7567,10 @@
         <v>754</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>1269</v>
+        <v>1246</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
@@ -7572,10 +7581,10 @@
         <v>755</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>1270</v>
+        <v>1295</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
@@ -7586,10 +7595,10 @@
         <v>756</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>1270</v>
+        <v>1295</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.25">
@@ -7600,10 +7609,10 @@
         <v>757</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>1271</v>
+        <v>1359</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
@@ -7614,10 +7623,10 @@
         <v>758</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>1272</v>
+        <v>1259</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.25">
@@ -7628,10 +7637,10 @@
         <v>759</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>1273</v>
+        <v>1320</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.25">
@@ -7642,10 +7651,10 @@
         <v>760</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>1225</v>
+        <v>1300</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.25">
@@ -7656,10 +7665,10 @@
         <v>761</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>1274</v>
+        <v>1319</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.25">
@@ -7670,10 +7679,10 @@
         <v>762</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>1275</v>
+        <v>1302</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
@@ -7684,10 +7693,10 @@
         <v>763</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>1276</v>
+        <v>1310</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
@@ -7698,10 +7707,10 @@
         <v>764</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>1277</v>
+        <v>1333</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
@@ -7712,10 +7721,10 @@
         <v>765</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>1278</v>
+        <v>1340</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.25">
@@ -7726,10 +7735,10 @@
         <v>766</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>1278</v>
+        <v>1340</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
@@ -7740,10 +7749,10 @@
         <v>767</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>1278</v>
+        <v>1340</v>
       </c>
       <c r="D211" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.25">
@@ -7754,10 +7763,10 @@
         <v>768</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>1279</v>
+        <v>1357</v>
       </c>
       <c r="D212" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
@@ -7768,10 +7777,10 @@
         <v>769</v>
       </c>
       <c r="C213" s="4" t="s">
-        <v>1279</v>
+        <v>1357</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
@@ -7782,10 +7791,10 @@
         <v>770</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="D214" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
@@ -7796,10 +7805,10 @@
         <v>771</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>1121</v>
+        <v>1158</v>
       </c>
       <c r="D215" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
@@ -7810,10 +7819,10 @@
         <v>772</v>
       </c>
       <c r="C216" s="4" t="s">
-        <v>1255</v>
+        <v>1239</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
@@ -7824,10 +7833,10 @@
         <v>773</v>
       </c>
       <c r="C217" s="4" t="s">
-        <v>1280</v>
+        <v>1304</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
@@ -7838,10 +7847,10 @@
         <v>774</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>1280</v>
+        <v>1304</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
@@ -7852,10 +7861,10 @@
         <v>775</v>
       </c>
       <c r="C219" s="4" t="s">
-        <v>1259</v>
+        <v>1209</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
@@ -7866,10 +7875,10 @@
         <v>776</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>1281</v>
+        <v>1214</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
@@ -7880,10 +7889,10 @@
         <v>777</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>1282</v>
+        <v>1213</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
@@ -7894,10 +7903,10 @@
         <v>778</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>1283</v>
+        <v>1327</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
@@ -7908,10 +7917,10 @@
         <v>779</v>
       </c>
       <c r="C223" s="4" t="s">
-        <v>1284</v>
+        <v>1426</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
@@ -7922,10 +7931,10 @@
         <v>780</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>1284</v>
+        <v>1426</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
@@ -7936,10 +7945,10 @@
         <v>781</v>
       </c>
       <c r="C225" s="4" t="s">
-        <v>1284</v>
+        <v>1426</v>
       </c>
       <c r="D225" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
@@ -7950,10 +7959,10 @@
         <v>782</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>1284</v>
+        <v>1426</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
@@ -7964,10 +7973,10 @@
         <v>783</v>
       </c>
       <c r="C227" s="4" t="s">
-        <v>1285</v>
+        <v>1199</v>
       </c>
       <c r="D227" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
@@ -7978,10 +7987,10 @@
         <v>784</v>
       </c>
       <c r="C228" s="4" t="s">
-        <v>1286</v>
+        <v>1282</v>
       </c>
       <c r="D228" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
@@ -7992,10 +8001,10 @@
         <v>785</v>
       </c>
       <c r="C229" s="4" t="s">
-        <v>1287</v>
+        <v>1273</v>
       </c>
       <c r="D229" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
@@ -8006,10 +8015,10 @@
         <v>786</v>
       </c>
       <c r="C230" s="4" t="s">
-        <v>1288</v>
+        <v>1425</v>
       </c>
       <c r="D230" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
@@ -8020,10 +8029,10 @@
         <v>787</v>
       </c>
       <c r="C231" s="4" t="s">
-        <v>1289</v>
+        <v>1323</v>
       </c>
       <c r="D231" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
@@ -8034,10 +8043,10 @@
         <v>788</v>
       </c>
       <c r="C232" s="4" t="s">
-        <v>1290</v>
+        <v>1169</v>
       </c>
       <c r="D232" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
@@ -8048,10 +8057,10 @@
         <v>789</v>
       </c>
       <c r="C233" s="4" t="s">
-        <v>1190</v>
+        <v>1171</v>
       </c>
       <c r="D233" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
@@ -8062,10 +8071,10 @@
         <v>790</v>
       </c>
       <c r="C234" s="4" t="s">
-        <v>1251</v>
+        <v>1292</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
@@ -8076,52 +8085,52 @@
         <v>791</v>
       </c>
       <c r="C235" s="4" t="s">
-        <v>1280</v>
+        <v>1304</v>
       </c>
       <c r="D235" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>1136</v>
+        <v>1121</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>1154</v>
+        <v>1139</v>
       </c>
       <c r="C236" s="4" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="D236" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
-        <v>1133</v>
+        <v>1118</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>1151</v>
+        <v>1136</v>
       </c>
       <c r="C237" s="4" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="D237" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>1132</v>
+        <v>1117</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>1150</v>
+        <v>1135</v>
       </c>
       <c r="C238" s="4" t="s">
-        <v>1445</v>
+        <v>1448</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
@@ -8132,10 +8141,10 @@
         <v>792</v>
       </c>
       <c r="C239" s="4" t="s">
-        <v>1291</v>
+        <v>1303</v>
       </c>
       <c r="D239" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
@@ -8146,10 +8155,10 @@
         <v>793</v>
       </c>
       <c r="C240" s="4" t="s">
-        <v>1292</v>
+        <v>1284</v>
       </c>
       <c r="D240" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
@@ -8160,10 +8169,10 @@
         <v>794</v>
       </c>
       <c r="C241" s="4" t="s">
-        <v>1293</v>
+        <v>1276</v>
       </c>
       <c r="D241" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
@@ -8174,10 +8183,10 @@
         <v>795</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>1251</v>
+        <v>1292</v>
       </c>
       <c r="D242" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
@@ -8188,10 +8197,10 @@
         <v>796</v>
       </c>
       <c r="C243" s="4" t="s">
-        <v>1294</v>
+        <v>1316</v>
       </c>
       <c r="D243" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
@@ -8202,10 +8211,10 @@
         <v>797</v>
       </c>
       <c r="C244" s="4" t="s">
-        <v>1280</v>
+        <v>1304</v>
       </c>
       <c r="D244" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
@@ -8216,10 +8225,10 @@
         <v>798</v>
       </c>
       <c r="C245" s="4" t="s">
-        <v>1295</v>
+        <v>1244</v>
       </c>
       <c r="D245" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
@@ -8230,10 +8239,10 @@
         <v>799</v>
       </c>
       <c r="C246" s="4" t="s">
-        <v>1296</v>
+        <v>1243</v>
       </c>
       <c r="D246" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
@@ -8244,10 +8253,10 @@
         <v>800</v>
       </c>
       <c r="C247" s="4" t="s">
-        <v>1297</v>
+        <v>1433</v>
       </c>
       <c r="D247" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
@@ -8258,10 +8267,10 @@
         <v>801</v>
       </c>
       <c r="C248" s="4" t="s">
-        <v>1298</v>
+        <v>1354</v>
       </c>
       <c r="D248" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
@@ -8272,10 +8281,10 @@
         <v>802</v>
       </c>
       <c r="C249" s="4" t="s">
-        <v>1299</v>
+        <v>1345</v>
       </c>
       <c r="D249" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
@@ -8286,10 +8295,10 @@
         <v>803</v>
       </c>
       <c r="C250" s="4" t="s">
-        <v>1300</v>
+        <v>1344</v>
       </c>
       <c r="D250" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
@@ -8300,10 +8309,10 @@
         <v>804</v>
       </c>
       <c r="C251" s="4" t="s">
-        <v>1220</v>
+        <v>1191</v>
       </c>
       <c r="D251" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
@@ -8314,10 +8323,10 @@
         <v>805</v>
       </c>
       <c r="C252" s="4" t="s">
-        <v>1301</v>
+        <v>1337</v>
       </c>
       <c r="D252" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
@@ -8328,10 +8337,10 @@
         <v>806</v>
       </c>
       <c r="C253" s="4" t="s">
-        <v>1301</v>
+        <v>1337</v>
       </c>
       <c r="D253" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
@@ -8342,10 +8351,10 @@
         <v>807</v>
       </c>
       <c r="C254" s="4" t="s">
-        <v>1290</v>
+        <v>1169</v>
       </c>
       <c r="D254" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
@@ -8356,10 +8365,10 @@
         <v>808</v>
       </c>
       <c r="C255" s="4" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D255" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
@@ -8370,10 +8379,10 @@
         <v>809</v>
       </c>
       <c r="C256" s="4" t="s">
-        <v>1303</v>
+        <v>1329</v>
       </c>
       <c r="D256" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
@@ -8384,10 +8393,10 @@
         <v>810</v>
       </c>
       <c r="C257" s="4" t="s">
-        <v>1304</v>
+        <v>1427</v>
       </c>
       <c r="D257" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
@@ -8398,10 +8407,10 @@
         <v>811</v>
       </c>
       <c r="C258" s="4" t="s">
-        <v>1305</v>
+        <v>1428</v>
       </c>
       <c r="D258" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
@@ -8412,10 +8421,10 @@
         <v>812</v>
       </c>
       <c r="C259" s="4" t="s">
-        <v>1306</v>
+        <v>1440</v>
       </c>
       <c r="D259" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
@@ -8426,10 +8435,10 @@
         <v>813</v>
       </c>
       <c r="C260" s="4" t="s">
-        <v>1307</v>
+        <v>1441</v>
       </c>
       <c r="D260" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
@@ -8440,10 +8449,10 @@
         <v>814</v>
       </c>
       <c r="C261" s="4" t="s">
-        <v>1293</v>
+        <v>1276</v>
       </c>
       <c r="D261" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
@@ -8454,10 +8463,10 @@
         <v>815</v>
       </c>
       <c r="C262" s="4" t="s">
-        <v>1195</v>
+        <v>1240</v>
       </c>
       <c r="D262" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
@@ -8468,10 +8477,10 @@
         <v>816</v>
       </c>
       <c r="C263" s="4" t="s">
-        <v>1308</v>
+        <v>1291</v>
       </c>
       <c r="D263" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
@@ -8482,10 +8491,10 @@
         <v>817</v>
       </c>
       <c r="C264" s="4" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="D264" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
@@ -8496,10 +8505,10 @@
         <v>818</v>
       </c>
       <c r="C265" s="4" t="s">
-        <v>1125</v>
+        <v>1162</v>
       </c>
       <c r="D265" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
@@ -8510,10 +8519,10 @@
         <v>819</v>
       </c>
       <c r="C266" s="4" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="D266" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
@@ -8524,10 +8533,10 @@
         <v>820</v>
       </c>
       <c r="C267" s="4" t="s">
-        <v>1310</v>
+        <v>1281</v>
       </c>
       <c r="D267" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
@@ -8538,10 +8547,10 @@
         <v>821</v>
       </c>
       <c r="C268" s="4" t="s">
-        <v>1311</v>
+        <v>1297</v>
       </c>
       <c r="D268" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
@@ -8552,10 +8561,10 @@
         <v>822</v>
       </c>
       <c r="C269" s="4" t="s">
-        <v>1204</v>
+        <v>1260</v>
       </c>
       <c r="D269" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
@@ -8566,10 +8575,10 @@
         <v>823</v>
       </c>
       <c r="C270" s="4" t="s">
-        <v>1312</v>
+        <v>1347</v>
       </c>
       <c r="D270" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
@@ -8580,10 +8589,10 @@
         <v>824</v>
       </c>
       <c r="C271" s="4" t="s">
-        <v>1313</v>
+        <v>1318</v>
       </c>
       <c r="D271" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
@@ -8594,10 +8603,10 @@
         <v>825</v>
       </c>
       <c r="C272" s="4" t="s">
-        <v>1314</v>
+        <v>1317</v>
       </c>
       <c r="D272" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
@@ -8608,10 +8617,10 @@
         <v>826</v>
       </c>
       <c r="C273" s="4" t="s">
-        <v>1315</v>
+        <v>1296</v>
       </c>
       <c r="D273" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
@@ -8622,10 +8631,10 @@
         <v>827</v>
       </c>
       <c r="C274" s="4" t="s">
-        <v>1315</v>
+        <v>1296</v>
       </c>
       <c r="D274" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
@@ -8636,24 +8645,24 @@
         <v>828</v>
       </c>
       <c r="C275" s="4" t="s">
-        <v>1316</v>
+        <v>1352</v>
       </c>
       <c r="D275" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" s="4" t="s">
-        <v>1139</v>
+        <v>1124</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>1157</v>
+        <v>1142</v>
       </c>
       <c r="C276" s="4" t="s">
-        <v>1214</v>
+        <v>1252</v>
       </c>
       <c r="D276" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
@@ -8664,10 +8673,10 @@
         <v>829</v>
       </c>
       <c r="C277" s="4" t="s">
-        <v>1317</v>
+        <v>1283</v>
       </c>
       <c r="D277" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
@@ -8678,10 +8687,10 @@
         <v>830</v>
       </c>
       <c r="C278" s="4" t="s">
-        <v>1318</v>
+        <v>1287</v>
       </c>
       <c r="D278" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
@@ -8692,10 +8701,10 @@
         <v>831</v>
       </c>
       <c r="C279" s="4" t="s">
-        <v>1248</v>
+        <v>1188</v>
       </c>
       <c r="D279" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
@@ -8706,10 +8715,10 @@
         <v>832</v>
       </c>
       <c r="C280" s="4" t="s">
-        <v>1319</v>
+        <v>1335</v>
       </c>
       <c r="D280" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
@@ -8720,10 +8729,10 @@
         <v>833</v>
       </c>
       <c r="C281" s="4" t="s">
-        <v>1198</v>
+        <v>1228</v>
       </c>
       <c r="D281" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
@@ -8734,10 +8743,10 @@
         <v>834</v>
       </c>
       <c r="C282" s="4" t="s">
-        <v>1320</v>
+        <v>1325</v>
       </c>
       <c r="D282" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
@@ -8748,10 +8757,10 @@
         <v>835</v>
       </c>
       <c r="C283" s="4" t="s">
-        <v>1321</v>
+        <v>1312</v>
       </c>
       <c r="D283" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
@@ -8762,10 +8771,10 @@
         <v>836</v>
       </c>
       <c r="C284" s="4" t="s">
-        <v>1205</v>
+        <v>1247</v>
       </c>
       <c r="D284" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
@@ -8776,10 +8785,10 @@
         <v>837</v>
       </c>
       <c r="C285" s="4" t="s">
-        <v>1130</v>
+        <v>1167</v>
       </c>
       <c r="D285" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
@@ -8790,10 +8799,10 @@
         <v>838</v>
       </c>
       <c r="C286" s="4" t="s">
-        <v>1322</v>
+        <v>1326</v>
       </c>
       <c r="D286" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
@@ -8804,10 +8813,10 @@
         <v>839</v>
       </c>
       <c r="C287" s="4" t="s">
-        <v>1129</v>
+        <v>1165</v>
       </c>
       <c r="D287" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
@@ -8818,24 +8827,24 @@
         <v>840</v>
       </c>
       <c r="C288" s="4" t="s">
-        <v>1323</v>
+        <v>1336</v>
       </c>
       <c r="D288" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" s="4" t="s">
-        <v>1135</v>
+        <v>1120</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>1153</v>
+        <v>1138</v>
       </c>
       <c r="C289" s="4" t="s">
-        <v>1448</v>
+        <v>1451</v>
       </c>
       <c r="D289" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
@@ -8846,10 +8855,10 @@
         <v>841</v>
       </c>
       <c r="C290" s="4" t="s">
-        <v>1290</v>
+        <v>1169</v>
       </c>
       <c r="D290" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
@@ -8860,10 +8869,10 @@
         <v>842</v>
       </c>
       <c r="C291" s="4" t="s">
-        <v>1290</v>
+        <v>1169</v>
       </c>
       <c r="D291" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
@@ -8874,10 +8883,10 @@
         <v>843</v>
       </c>
       <c r="C292" s="4" t="s">
-        <v>1211</v>
+        <v>1280</v>
       </c>
       <c r="D292" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
@@ -8888,10 +8897,10 @@
         <v>844</v>
       </c>
       <c r="C293" s="4" t="s">
-        <v>1259</v>
+        <v>1209</v>
       </c>
       <c r="D293" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
@@ -8902,10 +8911,10 @@
         <v>845</v>
       </c>
       <c r="C294" s="4" t="s">
-        <v>1324</v>
+        <v>1429</v>
       </c>
       <c r="D294" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
@@ -8916,10 +8925,10 @@
         <v>846</v>
       </c>
       <c r="C295" s="4" t="s">
-        <v>1325</v>
+        <v>1430</v>
       </c>
       <c r="D295" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
@@ -8930,10 +8939,10 @@
         <v>847</v>
       </c>
       <c r="C296" s="4" t="s">
-        <v>1326</v>
+        <v>1431</v>
       </c>
       <c r="D296" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
@@ -8944,10 +8953,10 @@
         <v>848</v>
       </c>
       <c r="C297" s="4" t="s">
-        <v>1327</v>
+        <v>1432</v>
       </c>
       <c r="D297" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
@@ -8958,10 +8967,10 @@
         <v>849</v>
       </c>
       <c r="C298" s="4" t="s">
-        <v>1328</v>
+        <v>1365</v>
       </c>
       <c r="D298" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
@@ -8972,10 +8981,10 @@
         <v>850</v>
       </c>
       <c r="C299" s="4" t="s">
-        <v>1329</v>
+        <v>1362</v>
       </c>
       <c r="D299" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
@@ -8986,10 +8995,10 @@
         <v>851</v>
       </c>
       <c r="C300" s="4" t="s">
-        <v>1329</v>
+        <v>1362</v>
       </c>
       <c r="D300" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
@@ -9000,10 +9009,10 @@
         <v>852</v>
       </c>
       <c r="C301" s="4" t="s">
-        <v>1330</v>
+        <v>1367</v>
       </c>
       <c r="D301" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
@@ -9014,10 +9023,10 @@
         <v>853</v>
       </c>
       <c r="C302" s="4" t="s">
-        <v>1331</v>
+        <v>1370</v>
       </c>
       <c r="D302" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
@@ -9028,10 +9037,10 @@
         <v>854</v>
       </c>
       <c r="C303" s="4" t="s">
-        <v>1121</v>
+        <v>1158</v>
       </c>
       <c r="D303" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
@@ -9042,10 +9051,10 @@
         <v>855</v>
       </c>
       <c r="C304" s="4" t="s">
-        <v>1243</v>
+        <v>1201</v>
       </c>
       <c r="D304" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
@@ -9056,10 +9065,10 @@
         <v>856</v>
       </c>
       <c r="C305" s="4" t="s">
-        <v>1322</v>
+        <v>1326</v>
       </c>
       <c r="D305" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
@@ -9070,10 +9079,10 @@
         <v>857</v>
       </c>
       <c r="C306" s="4" t="s">
-        <v>1332</v>
+        <v>1349</v>
       </c>
       <c r="D306" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
@@ -9084,10 +9093,10 @@
         <v>858</v>
       </c>
       <c r="C307" s="4" t="s">
-        <v>1332</v>
+        <v>1349</v>
       </c>
       <c r="D307" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
@@ -9098,10 +9107,10 @@
         <v>859</v>
       </c>
       <c r="C308" s="4" t="s">
-        <v>1333</v>
+        <v>1338</v>
       </c>
       <c r="D308" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
@@ -9112,10 +9121,10 @@
         <v>860</v>
       </c>
       <c r="C309" s="4" t="s">
-        <v>1333</v>
+        <v>1338</v>
       </c>
       <c r="D309" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
@@ -9126,10 +9135,10 @@
         <v>861</v>
       </c>
       <c r="C310" s="4" t="s">
-        <v>1334</v>
+        <v>1341</v>
       </c>
       <c r="D310" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
@@ -9140,10 +9149,10 @@
         <v>862</v>
       </c>
       <c r="C311" s="4" t="s">
-        <v>1334</v>
+        <v>1341</v>
       </c>
       <c r="D311" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
@@ -9154,10 +9163,10 @@
         <v>863</v>
       </c>
       <c r="C312" s="4" t="s">
-        <v>1335</v>
+        <v>1306</v>
       </c>
       <c r="D312" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
@@ -9168,10 +9177,10 @@
         <v>864</v>
       </c>
       <c r="C313" s="4" t="s">
-        <v>1336</v>
+        <v>1331</v>
       </c>
       <c r="D313" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
@@ -9182,10 +9191,10 @@
         <v>865</v>
       </c>
       <c r="C314" s="4" t="s">
-        <v>1337</v>
+        <v>1346</v>
       </c>
       <c r="D314" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
@@ -9196,10 +9205,10 @@
         <v>866</v>
       </c>
       <c r="C315" s="4" t="s">
-        <v>1337</v>
+        <v>1346</v>
       </c>
       <c r="D315" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
@@ -9210,10 +9219,10 @@
         <v>867</v>
       </c>
       <c r="C316" s="4" t="s">
-        <v>1281</v>
+        <v>1214</v>
       </c>
       <c r="D316" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
@@ -9224,10 +9233,10 @@
         <v>868</v>
       </c>
       <c r="C317" s="4" t="s">
-        <v>1281</v>
+        <v>1214</v>
       </c>
       <c r="D317" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
@@ -9238,10 +9247,10 @@
         <v>869</v>
       </c>
       <c r="C318" s="4" t="s">
-        <v>1338</v>
+        <v>1334</v>
       </c>
       <c r="D318" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
@@ -9252,10 +9261,10 @@
         <v>870</v>
       </c>
       <c r="C319" s="4" t="s">
-        <v>1339</v>
+        <v>1350</v>
       </c>
       <c r="D319" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
@@ -9266,10 +9275,10 @@
         <v>871</v>
       </c>
       <c r="C320" s="4" t="s">
-        <v>1270</v>
+        <v>1295</v>
       </c>
       <c r="D320" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
@@ -9280,10 +9289,10 @@
         <v>872</v>
       </c>
       <c r="C321" s="4" t="s">
-        <v>1125</v>
+        <v>1162</v>
       </c>
       <c r="D321" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
@@ -9294,10 +9303,10 @@
         <v>873</v>
       </c>
       <c r="C322" s="4" t="s">
-        <v>1125</v>
+        <v>1162</v>
       </c>
       <c r="D322" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
@@ -9308,10 +9317,10 @@
         <v>874</v>
       </c>
       <c r="C323" s="4" t="s">
-        <v>1340</v>
+        <v>1237</v>
       </c>
       <c r="D323" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
@@ -9322,10 +9331,10 @@
         <v>875</v>
       </c>
       <c r="C324" s="4" t="s">
-        <v>1341</v>
+        <v>1435</v>
       </c>
       <c r="D324" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
@@ -9336,10 +9345,10 @@
         <v>876</v>
       </c>
       <c r="C325" s="4" t="s">
-        <v>1342</v>
+        <v>1434</v>
       </c>
       <c r="D325" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
@@ -9350,10 +9359,10 @@
         <v>877</v>
       </c>
       <c r="C326" s="4" t="s">
-        <v>1275</v>
+        <v>1302</v>
       </c>
       <c r="D326" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
@@ -9364,10 +9373,10 @@
         <v>878</v>
       </c>
       <c r="C327" s="4" t="s">
-        <v>1272</v>
+        <v>1259</v>
       </c>
       <c r="D327" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
@@ -9378,10 +9387,10 @@
         <v>879</v>
       </c>
       <c r="C328" s="4" t="s">
-        <v>1343</v>
+        <v>1339</v>
       </c>
       <c r="D328" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
@@ -9392,10 +9401,10 @@
         <v>880</v>
       </c>
       <c r="C329" s="4" t="s">
-        <v>1343</v>
+        <v>1339</v>
       </c>
       <c r="D329" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
@@ -9406,10 +9415,10 @@
         <v>881</v>
       </c>
       <c r="C330" s="4" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
       <c r="D330" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
@@ -9420,10 +9429,10 @@
         <v>882</v>
       </c>
       <c r="C331" s="4" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
       <c r="D331" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
@@ -9434,10 +9443,10 @@
         <v>883</v>
       </c>
       <c r="C332" s="4" t="s">
-        <v>1344</v>
+        <v>1358</v>
       </c>
       <c r="D332" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
@@ -9448,10 +9457,10 @@
         <v>884</v>
       </c>
       <c r="C333" s="4" t="s">
-        <v>1344</v>
+        <v>1358</v>
       </c>
       <c r="D333" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
@@ -9462,10 +9471,10 @@
         <v>885</v>
       </c>
       <c r="C334" s="4" t="s">
-        <v>1345</v>
+        <v>1353</v>
       </c>
       <c r="D334" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
@@ -9476,10 +9485,10 @@
         <v>886</v>
       </c>
       <c r="C335" s="4" t="s">
-        <v>1345</v>
+        <v>1353</v>
       </c>
       <c r="D335" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
@@ -9490,10 +9499,10 @@
         <v>887</v>
       </c>
       <c r="C336" s="4" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="D336" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
@@ -9504,10 +9513,10 @@
         <v>888</v>
       </c>
       <c r="C337" s="4" t="s">
-        <v>1268</v>
+        <v>1308</v>
       </c>
       <c r="D337" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
@@ -9518,10 +9527,10 @@
         <v>889</v>
       </c>
       <c r="C338" s="4" t="s">
-        <v>1308</v>
+        <v>1291</v>
       </c>
       <c r="D338" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
@@ -9532,10 +9541,10 @@
         <v>890</v>
       </c>
       <c r="C339" s="4" t="s">
-        <v>1346</v>
+        <v>1442</v>
       </c>
       <c r="D339" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
@@ -9546,10 +9555,10 @@
         <v>891</v>
       </c>
       <c r="C340" s="4" t="s">
-        <v>1347</v>
+        <v>1443</v>
       </c>
       <c r="D340" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
@@ -9560,10 +9569,10 @@
         <v>892</v>
       </c>
       <c r="C341" s="4" t="s">
-        <v>1348</v>
+        <v>1447</v>
       </c>
       <c r="D341" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
@@ -9574,10 +9583,10 @@
         <v>893</v>
       </c>
       <c r="C342" s="4" t="s">
-        <v>1349</v>
+        <v>1445</v>
       </c>
       <c r="D342" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
@@ -9588,10 +9597,10 @@
         <v>894</v>
       </c>
       <c r="C343" s="4" t="s">
-        <v>1350</v>
+        <v>1446</v>
       </c>
       <c r="D343" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
@@ -9602,10 +9611,10 @@
         <v>895</v>
       </c>
       <c r="C344" s="4" t="s">
-        <v>1351</v>
+        <v>1444</v>
       </c>
       <c r="D344" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
@@ -9616,10 +9625,10 @@
         <v>896</v>
       </c>
       <c r="C345" s="4" t="s">
-        <v>1119</v>
+        <v>1156</v>
       </c>
       <c r="D345" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
@@ -9630,10 +9639,10 @@
         <v>897</v>
       </c>
       <c r="C346" s="4" t="s">
-        <v>1119</v>
+        <v>1156</v>
       </c>
       <c r="D346" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
@@ -9644,10 +9653,10 @@
         <v>898</v>
       </c>
       <c r="C347" s="4" t="s">
-        <v>1258</v>
+        <v>1324</v>
       </c>
       <c r="D347" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
@@ -9658,10 +9667,10 @@
         <v>899</v>
       </c>
       <c r="C348" s="4" t="s">
-        <v>1258</v>
+        <v>1324</v>
       </c>
       <c r="D348" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.25">
@@ -9672,66 +9681,66 @@
         <v>900</v>
       </c>
       <c r="C349" s="4" t="s">
-        <v>1320</v>
+        <v>1325</v>
       </c>
       <c r="D349" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" s="4" t="s">
-        <v>1147</v>
+        <v>1132</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>1165</v>
+        <v>1150</v>
       </c>
       <c r="C350" s="4" t="s">
-        <v>1364</v>
+        <v>1361</v>
       </c>
       <c r="D350" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" s="4" t="s">
-        <v>1146</v>
+        <v>1131</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>1164</v>
+        <v>1149</v>
       </c>
       <c r="C351" s="4" t="s">
-        <v>1454</v>
+        <v>1457</v>
       </c>
       <c r="D351" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" s="4" t="s">
-        <v>1144</v>
+        <v>1129</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>1162</v>
+        <v>1147</v>
       </c>
       <c r="C352" s="4" t="s">
-        <v>1235</v>
+        <v>1293</v>
       </c>
       <c r="D352" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A353" s="4" t="s">
-        <v>1141</v>
+        <v>1126</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>1159</v>
+        <v>1144</v>
       </c>
       <c r="C353" s="4" t="s">
-        <v>1128</v>
+        <v>1164</v>
       </c>
       <c r="D353" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.25">
@@ -9742,10 +9751,10 @@
         <v>901</v>
       </c>
       <c r="C354" s="4" t="s">
-        <v>1121</v>
+        <v>1158</v>
       </c>
       <c r="D354" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.25">
@@ -9756,10 +9765,10 @@
         <v>902</v>
       </c>
       <c r="C355" s="4" t="s">
-        <v>1352</v>
+        <v>1436</v>
       </c>
       <c r="D355" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.25">
@@ -9770,10 +9779,10 @@
         <v>903</v>
       </c>
       <c r="C356" s="4" t="s">
-        <v>1353</v>
+        <v>1439</v>
       </c>
       <c r="D356" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.25">
@@ -9784,10 +9793,10 @@
         <v>904</v>
       </c>
       <c r="C357" s="4" t="s">
-        <v>1354</v>
+        <v>1364</v>
       </c>
       <c r="D357" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.25">
@@ -9798,10 +9807,10 @@
         <v>905</v>
       </c>
       <c r="C358" s="4" t="s">
-        <v>1225</v>
+        <v>1300</v>
       </c>
       <c r="D358" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
@@ -9812,10 +9821,10 @@
         <v>906</v>
       </c>
       <c r="C359" s="4" t="s">
-        <v>1225</v>
+        <v>1300</v>
       </c>
       <c r="D359" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.25">
@@ -9826,10 +9835,10 @@
         <v>907</v>
       </c>
       <c r="C360" s="4" t="s">
-        <v>1355</v>
+        <v>1363</v>
       </c>
       <c r="D360" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.25">
@@ -9840,10 +9849,10 @@
         <v>908</v>
       </c>
       <c r="C361" s="4" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="D361" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
@@ -9854,10 +9863,10 @@
         <v>909</v>
       </c>
       <c r="C362" s="4" t="s">
-        <v>1357</v>
+        <v>1311</v>
       </c>
       <c r="D362" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.25">
@@ -9868,10 +9877,10 @@
         <v>910</v>
       </c>
       <c r="C363" s="4" t="s">
-        <v>1188</v>
+        <v>1202</v>
       </c>
       <c r="D363" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.25">
@@ -9882,10 +9891,10 @@
         <v>911</v>
       </c>
       <c r="C364" s="4" t="s">
-        <v>1358</v>
+        <v>1220</v>
       </c>
       <c r="D364" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.25">
@@ -9896,10 +9905,10 @@
         <v>912</v>
       </c>
       <c r="C365" s="4" t="s">
-        <v>1359</v>
+        <v>1236</v>
       </c>
       <c r="D365" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.25">
@@ -9910,10 +9919,10 @@
         <v>913</v>
       </c>
       <c r="C366" s="4" t="s">
-        <v>1258</v>
+        <v>1324</v>
       </c>
       <c r="D366" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.25">
@@ -9924,10 +9933,10 @@
         <v>914</v>
       </c>
       <c r="C367" s="4" t="s">
-        <v>1278</v>
+        <v>1340</v>
       </c>
       <c r="D367" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.25">
@@ -9938,10 +9947,10 @@
         <v>915</v>
       </c>
       <c r="C368" s="4" t="s">
-        <v>1278</v>
+        <v>1340</v>
       </c>
       <c r="D368" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.25">
@@ -9952,10 +9961,10 @@
         <v>916</v>
       </c>
       <c r="C369" s="4" t="s">
-        <v>1278</v>
+        <v>1340</v>
       </c>
       <c r="D369" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.25">
@@ -9966,10 +9975,10 @@
         <v>917</v>
       </c>
       <c r="C370" s="4" t="s">
-        <v>1360</v>
+        <v>1348</v>
       </c>
       <c r="D370" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.25">
@@ -9980,10 +9989,10 @@
         <v>918</v>
       </c>
       <c r="C371" s="4" t="s">
-        <v>1361</v>
+        <v>1321</v>
       </c>
       <c r="D371" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.25">
@@ -9994,10 +10003,10 @@
         <v>919</v>
       </c>
       <c r="C372" s="4" t="s">
-        <v>1361</v>
+        <v>1321</v>
       </c>
       <c r="D372" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.25">
@@ -10008,10 +10017,10 @@
         <v>920</v>
       </c>
       <c r="C373" s="4" t="s">
-        <v>1362</v>
+        <v>1351</v>
       </c>
       <c r="D373" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.25">
@@ -10022,10 +10031,10 @@
         <v>921</v>
       </c>
       <c r="C374" s="4" t="s">
-        <v>1198</v>
+        <v>1228</v>
       </c>
       <c r="D374" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.25">
@@ -10036,10 +10045,10 @@
         <v>922</v>
       </c>
       <c r="C375" s="4" t="s">
-        <v>1198</v>
+        <v>1228</v>
       </c>
       <c r="D375" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.25">
@@ -10050,10 +10059,10 @@
         <v>923</v>
       </c>
       <c r="C376" s="4" t="s">
-        <v>1293</v>
+        <v>1276</v>
       </c>
       <c r="D376" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.25">
@@ -10064,10 +10073,10 @@
         <v>924</v>
       </c>
       <c r="C377" s="4" t="s">
-        <v>1115</v>
+        <v>1153</v>
       </c>
       <c r="D377" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.25">
@@ -10078,10 +10087,10 @@
         <v>925</v>
       </c>
       <c r="C378" s="4" t="s">
-        <v>1363</v>
+        <v>1342</v>
       </c>
       <c r="D378" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.25">
@@ -10092,10 +10101,10 @@
         <v>926</v>
       </c>
       <c r="C379" s="4" t="s">
-        <v>1363</v>
+        <v>1342</v>
       </c>
       <c r="D379" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.25">
@@ -10106,10 +10115,10 @@
         <v>927</v>
       </c>
       <c r="C380" s="4" t="s">
-        <v>1364</v>
+        <v>1361</v>
       </c>
       <c r="D380" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.25">
@@ -10120,10 +10129,10 @@
         <v>928</v>
       </c>
       <c r="C381" s="4" t="s">
-        <v>1277</v>
+        <v>1333</v>
       </c>
       <c r="D381" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.25">
@@ -10134,10 +10143,10 @@
         <v>929</v>
       </c>
       <c r="C382" s="4" t="s">
-        <v>1130</v>
+        <v>1167</v>
       </c>
       <c r="D382" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.25">
@@ -10148,10 +10157,10 @@
         <v>930</v>
       </c>
       <c r="C383" s="4" t="s">
-        <v>1239</v>
+        <v>1313</v>
       </c>
       <c r="D383" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.25">
@@ -10162,10 +10171,10 @@
         <v>931</v>
       </c>
       <c r="C384" s="4" t="s">
-        <v>1216</v>
+        <v>1248</v>
       </c>
       <c r="D384" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.25">
@@ -10176,10 +10185,10 @@
         <v>932</v>
       </c>
       <c r="C385" s="4" t="s">
-        <v>1201</v>
+        <v>1182</v>
       </c>
       <c r="D385" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.25">
@@ -10190,10 +10199,10 @@
         <v>933</v>
       </c>
       <c r="C386" s="4" t="s">
-        <v>1243</v>
+        <v>1201</v>
       </c>
       <c r="D386" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.25">
@@ -10204,10 +10213,10 @@
         <v>934</v>
       </c>
       <c r="C387" s="4" t="s">
-        <v>1282</v>
+        <v>1213</v>
       </c>
       <c r="D387" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.25">
@@ -10218,10 +10227,10 @@
         <v>935</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>1365</v>
+        <v>1221</v>
       </c>
       <c r="D388" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.25">
@@ -10232,10 +10241,10 @@
         <v>936</v>
       </c>
       <c r="C389" s="4" t="s">
-        <v>1366</v>
+        <v>1330</v>
       </c>
       <c r="D389" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.25">
@@ -10246,10 +10255,10 @@
         <v>937</v>
       </c>
       <c r="C390" s="4" t="s">
-        <v>1122</v>
+        <v>1159</v>
       </c>
       <c r="D390" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.25">
@@ -10260,10 +10269,10 @@
         <v>938</v>
       </c>
       <c r="C391" s="4" t="s">
-        <v>1367</v>
+        <v>1328</v>
       </c>
       <c r="D391" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.25">
@@ -10274,10 +10283,10 @@
         <v>939</v>
       </c>
       <c r="C392" s="4" t="s">
-        <v>1368</v>
+        <v>1343</v>
       </c>
       <c r="D392" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.25">
@@ -10288,10 +10297,10 @@
         <v>940</v>
       </c>
       <c r="C393" s="4" t="s">
-        <v>1369</v>
+        <v>1360</v>
       </c>
       <c r="D393" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.25">
@@ -10302,10 +10311,10 @@
         <v>941</v>
       </c>
       <c r="C394" s="4" t="s">
-        <v>1221</v>
+        <v>1189</v>
       </c>
       <c r="D394" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.25">
@@ -10316,10 +10325,10 @@
         <v>942</v>
       </c>
       <c r="C395" s="4" t="s">
-        <v>1334</v>
+        <v>1341</v>
       </c>
       <c r="D395" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.25">
@@ -10330,10 +10339,10 @@
         <v>943</v>
       </c>
       <c r="C396" s="4" t="s">
-        <v>1283</v>
+        <v>1327</v>
       </c>
       <c r="D396" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.25">
@@ -10344,10 +10353,10 @@
         <v>944</v>
       </c>
       <c r="C397" s="4" t="s">
-        <v>1283</v>
+        <v>1327</v>
       </c>
       <c r="D397" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.25">
@@ -10358,10 +10367,10 @@
         <v>945</v>
       </c>
       <c r="C398" s="4" t="s">
-        <v>1283</v>
+        <v>1327</v>
       </c>
       <c r="D398" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.25">
@@ -10372,10 +10381,10 @@
         <v>946</v>
       </c>
       <c r="C399" s="4" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="D399" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.25">
@@ -10386,10 +10395,10 @@
         <v>947</v>
       </c>
       <c r="C400" s="4" t="s">
-        <v>1371</v>
+        <v>1356</v>
       </c>
       <c r="D400" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.25">
@@ -10400,10 +10409,10 @@
         <v>948</v>
       </c>
       <c r="C401" s="4" t="s">
-        <v>1372</v>
+        <v>1222</v>
       </c>
       <c r="D401" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.25">
@@ -10414,10 +10423,10 @@
         <v>949</v>
       </c>
       <c r="C402" s="4" t="s">
-        <v>1373</v>
+        <v>1385</v>
       </c>
       <c r="D402" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.25">
@@ -10428,10 +10437,10 @@
         <v>950</v>
       </c>
       <c r="C403" s="4" t="s">
-        <v>1374</v>
+        <v>1438</v>
       </c>
       <c r="D403" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.25">
@@ -10442,10 +10451,10 @@
         <v>951</v>
       </c>
       <c r="C404" s="4" t="s">
-        <v>1375</v>
+        <v>1437</v>
       </c>
       <c r="D404" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.25">
@@ -10456,52 +10465,52 @@
         <v>952</v>
       </c>
       <c r="C405" s="4" t="s">
-        <v>1194</v>
+        <v>1175</v>
       </c>
       <c r="D405" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A406" s="4" t="s">
-        <v>1148</v>
+        <v>1133</v>
       </c>
       <c r="B406" s="4" t="s">
-        <v>1166</v>
+        <v>1151</v>
       </c>
       <c r="C406" s="4" t="s">
-        <v>1393</v>
+        <v>1383</v>
       </c>
       <c r="D406" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A407" s="4" t="s">
-        <v>1149</v>
+        <v>1134</v>
       </c>
       <c r="B407" s="4" t="s">
-        <v>1167</v>
+        <v>1152</v>
       </c>
       <c r="C407" s="4" t="s">
-        <v>1455</v>
+        <v>1458</v>
       </c>
       <c r="D407" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A408" s="4" t="s">
-        <v>1142</v>
+        <v>1127</v>
       </c>
       <c r="B408" s="4" t="s">
-        <v>1160</v>
+        <v>1145</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="D408" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.25">
@@ -10512,10 +10521,10 @@
         <v>953</v>
       </c>
       <c r="C409" s="4" t="s">
-        <v>1376</v>
+        <v>1387</v>
       </c>
       <c r="D409" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.25">
@@ -10526,10 +10535,10 @@
         <v>954</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>1377</v>
+        <v>1371</v>
       </c>
       <c r="D410" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.25">
@@ -10540,10 +10549,10 @@
         <v>955</v>
       </c>
       <c r="C411" s="4" t="s">
-        <v>1377</v>
+        <v>1371</v>
       </c>
       <c r="D411" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.25">
@@ -10554,10 +10563,10 @@
         <v>956</v>
       </c>
       <c r="C412" s="4" t="s">
-        <v>1378</v>
+        <v>1373</v>
       </c>
       <c r="D412" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.25">
@@ -10568,10 +10577,10 @@
         <v>957</v>
       </c>
       <c r="C413" s="4" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D413" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.25">
@@ -10585,7 +10594,7 @@
         <v>1379</v>
       </c>
       <c r="D414" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.25">
@@ -10596,10 +10605,10 @@
         <v>959</v>
       </c>
       <c r="C415" s="4" t="s">
-        <v>1186</v>
+        <v>1245</v>
       </c>
       <c r="D415" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.25">
@@ -10610,10 +10619,10 @@
         <v>960</v>
       </c>
       <c r="C416" s="4" t="s">
-        <v>1290</v>
+        <v>1169</v>
       </c>
       <c r="D416" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.25">
@@ -10624,10 +10633,10 @@
         <v>961</v>
       </c>
       <c r="C417" s="4" t="s">
-        <v>1380</v>
+        <v>1223</v>
       </c>
       <c r="D417" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.25">
@@ -10638,10 +10647,10 @@
         <v>962</v>
       </c>
       <c r="C418" s="4" t="s">
-        <v>1381</v>
+        <v>1374</v>
       </c>
       <c r="D418" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.25">
@@ -10652,10 +10661,10 @@
         <v>963</v>
       </c>
       <c r="C419" s="4" t="s">
-        <v>1258</v>
+        <v>1324</v>
       </c>
       <c r="D419" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.25">
@@ -10666,10 +10675,10 @@
         <v>964</v>
       </c>
       <c r="C420" s="4" t="s">
-        <v>1382</v>
+        <v>1366</v>
       </c>
       <c r="D420" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.25">
@@ -10680,10 +10689,10 @@
         <v>965</v>
       </c>
       <c r="C421" s="4" t="s">
-        <v>1188</v>
+        <v>1202</v>
       </c>
       <c r="D421" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.25">
@@ -10694,10 +10703,10 @@
         <v>966</v>
       </c>
       <c r="C422" s="4" t="s">
-        <v>1220</v>
+        <v>1191</v>
       </c>
       <c r="D422" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.25">
@@ -10708,10 +10717,10 @@
         <v>967</v>
       </c>
       <c r="C423" s="4" t="s">
-        <v>1383</v>
+        <v>1372</v>
       </c>
       <c r="D423" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.25">
@@ -10722,10 +10731,10 @@
         <v>968</v>
       </c>
       <c r="C424" s="4" t="s">
-        <v>1384</v>
+        <v>1258</v>
       </c>
       <c r="D424" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.25">
@@ -10736,10 +10745,10 @@
         <v>969</v>
       </c>
       <c r="C425" s="4" t="s">
-        <v>1367</v>
+        <v>1328</v>
       </c>
       <c r="D425" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.25">
@@ -10750,10 +10759,10 @@
         <v>970</v>
       </c>
       <c r="C426" s="4" t="s">
-        <v>1367</v>
+        <v>1328</v>
       </c>
       <c r="D426" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.25">
@@ -10764,10 +10773,10 @@
         <v>971</v>
       </c>
       <c r="C427" s="4" t="s">
-        <v>1367</v>
+        <v>1328</v>
       </c>
       <c r="D427" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.25">
@@ -10778,10 +10787,10 @@
         <v>972</v>
       </c>
       <c r="C428" s="4" t="s">
-        <v>1188</v>
+        <v>1202</v>
       </c>
       <c r="D428" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.25">
@@ -10792,10 +10801,10 @@
         <v>973</v>
       </c>
       <c r="C429" s="4" t="s">
-        <v>1202</v>
+        <v>1207</v>
       </c>
       <c r="D429" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.25">
@@ -10806,10 +10815,10 @@
         <v>974</v>
       </c>
       <c r="C430" s="4" t="s">
-        <v>1233</v>
+        <v>1315</v>
       </c>
       <c r="D430" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.25">
@@ -10820,10 +10829,10 @@
         <v>975</v>
       </c>
       <c r="C431" s="4" t="s">
-        <v>1385</v>
+        <v>1253</v>
       </c>
       <c r="D431" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.25">
@@ -10834,10 +10843,10 @@
         <v>976</v>
       </c>
       <c r="C432" s="4" t="s">
-        <v>1331</v>
+        <v>1370</v>
       </c>
       <c r="D432" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.25">
@@ -10848,10 +10857,10 @@
         <v>977</v>
       </c>
       <c r="C433" s="4" t="s">
-        <v>1126</v>
+        <v>1386</v>
       </c>
       <c r="D433" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="434" spans="1:4" x14ac:dyDescent="0.25">
@@ -10862,10 +10871,10 @@
         <v>978</v>
       </c>
       <c r="C434" s="4" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
       <c r="D434" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.25">
@@ -10876,10 +10885,10 @@
         <v>979</v>
       </c>
       <c r="C435" s="4" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="D435" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.25">
@@ -10890,10 +10899,10 @@
         <v>980</v>
       </c>
       <c r="C436" s="4" t="s">
-        <v>1127</v>
+        <v>1163</v>
       </c>
       <c r="D436" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="437" spans="1:4" x14ac:dyDescent="0.25">
@@ -10904,10 +10913,10 @@
         <v>981</v>
       </c>
       <c r="C437" s="4" t="s">
-        <v>1238</v>
+        <v>1269</v>
       </c>
       <c r="D437" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="438" spans="1:4" x14ac:dyDescent="0.25">
@@ -10918,10 +10927,10 @@
         <v>982</v>
       </c>
       <c r="C438" s="4" t="s">
-        <v>1387</v>
+        <v>1368</v>
       </c>
       <c r="D438" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.25">
@@ -10932,10 +10941,10 @@
         <v>983</v>
       </c>
       <c r="C439" s="4" t="s">
-        <v>1265</v>
+        <v>1198</v>
       </c>
       <c r="D439" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="440" spans="1:4" x14ac:dyDescent="0.25">
@@ -10946,10 +10955,10 @@
         <v>984</v>
       </c>
       <c r="C440" s="4" t="s">
-        <v>1197</v>
+        <v>1185</v>
       </c>
       <c r="D440" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="441" spans="1:4" x14ac:dyDescent="0.25">
@@ -10960,10 +10969,10 @@
         <v>985</v>
       </c>
       <c r="C441" s="4" t="s">
-        <v>1197</v>
+        <v>1185</v>
       </c>
       <c r="D441" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.25">
@@ -10974,10 +10983,10 @@
         <v>986</v>
       </c>
       <c r="C442" s="4" t="s">
-        <v>1197</v>
+        <v>1185</v>
       </c>
       <c r="D442" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="443" spans="1:4" x14ac:dyDescent="0.25">
@@ -10988,10 +10997,10 @@
         <v>987</v>
       </c>
       <c r="C443" s="4" t="s">
-        <v>1197</v>
+        <v>1185</v>
       </c>
       <c r="D443" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="444" spans="1:4" x14ac:dyDescent="0.25">
@@ -11002,10 +11011,10 @@
         <v>988</v>
       </c>
       <c r="C444" s="4" t="s">
-        <v>1197</v>
+        <v>1185</v>
       </c>
       <c r="D444" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="445" spans="1:4" x14ac:dyDescent="0.25">
@@ -11016,10 +11025,10 @@
         <v>989</v>
       </c>
       <c r="C445" s="4" t="s">
-        <v>1373</v>
+        <v>1385</v>
       </c>
       <c r="D445" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="446" spans="1:4" x14ac:dyDescent="0.25">
@@ -11030,10 +11039,10 @@
         <v>990</v>
       </c>
       <c r="C446" s="4" t="s">
-        <v>1388</v>
+        <v>1375</v>
       </c>
       <c r="D446" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="447" spans="1:4" x14ac:dyDescent="0.25">
@@ -11044,10 +11053,10 @@
         <v>991</v>
       </c>
       <c r="C447" s="4" t="s">
-        <v>1388</v>
+        <v>1375</v>
       </c>
       <c r="D447" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.25">
@@ -11058,10 +11067,10 @@
         <v>992</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>1388</v>
+        <v>1375</v>
       </c>
       <c r="D448" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.25">
@@ -11072,10 +11081,10 @@
         <v>993</v>
       </c>
       <c r="C449" s="4" t="s">
-        <v>1388</v>
+        <v>1375</v>
       </c>
       <c r="D449" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.25">
@@ -11086,10 +11095,10 @@
         <v>994</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>1389</v>
+        <v>1378</v>
       </c>
       <c r="D450" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.25">
@@ -11100,10 +11109,10 @@
         <v>995</v>
       </c>
       <c r="C451" s="4" t="s">
-        <v>1388</v>
+        <v>1375</v>
       </c>
       <c r="D451" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.25">
@@ -11114,10 +11123,10 @@
         <v>996</v>
       </c>
       <c r="C452" s="4" t="s">
-        <v>1390</v>
+        <v>1377</v>
       </c>
       <c r="D452" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.25">
@@ -11128,10 +11137,10 @@
         <v>997</v>
       </c>
       <c r="C453" s="4" t="s">
-        <v>1390</v>
+        <v>1377</v>
       </c>
       <c r="D453" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.25">
@@ -11142,10 +11151,10 @@
         <v>998</v>
       </c>
       <c r="C454" s="4" t="s">
-        <v>1390</v>
+        <v>1377</v>
       </c>
       <c r="D454" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.25">
@@ -11156,10 +11165,10 @@
         <v>999</v>
       </c>
       <c r="C455" s="4" t="s">
-        <v>1390</v>
+        <v>1377</v>
       </c>
       <c r="D455" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.25">
@@ -11170,10 +11179,10 @@
         <v>1000</v>
       </c>
       <c r="C456" s="4" t="s">
-        <v>1390</v>
+        <v>1377</v>
       </c>
       <c r="D456" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.25">
@@ -11184,10 +11193,10 @@
         <v>1001</v>
       </c>
       <c r="C457" s="4" t="s">
-        <v>1388</v>
+        <v>1375</v>
       </c>
       <c r="D457" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.25">
@@ -11198,10 +11207,10 @@
         <v>1002</v>
       </c>
       <c r="C458" s="4" t="s">
-        <v>1388</v>
+        <v>1375</v>
       </c>
       <c r="D458" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.25">
@@ -11212,10 +11221,10 @@
         <v>1003</v>
       </c>
       <c r="C459" s="4" t="s">
-        <v>1388</v>
+        <v>1375</v>
       </c>
       <c r="D459" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.25">
@@ -11226,10 +11235,10 @@
         <v>1004</v>
       </c>
       <c r="C460" s="4" t="s">
-        <v>1388</v>
+        <v>1375</v>
       </c>
       <c r="D460" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.25">
@@ -11240,10 +11249,10 @@
         <v>1005</v>
       </c>
       <c r="C461" s="4" t="s">
-        <v>1388</v>
+        <v>1375</v>
       </c>
       <c r="D461" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.25">
@@ -11254,10 +11263,10 @@
         <v>1006</v>
       </c>
       <c r="C462" s="4" t="s">
-        <v>1388</v>
+        <v>1375</v>
       </c>
       <c r="D462" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.25">
@@ -11268,10 +11277,10 @@
         <v>1007</v>
       </c>
       <c r="C463" s="4" t="s">
-        <v>1391</v>
+        <v>1224</v>
       </c>
       <c r="D463" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.25">
@@ -11282,10 +11291,10 @@
         <v>1008</v>
       </c>
       <c r="C464" s="4" t="s">
-        <v>1392</v>
+        <v>1208</v>
       </c>
       <c r="D464" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.25">
@@ -11296,10 +11305,10 @@
         <v>1009</v>
       </c>
       <c r="C465" s="4" t="s">
-        <v>1393</v>
+        <v>1383</v>
       </c>
       <c r="D465" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.25">
@@ -11310,10 +11319,10 @@
         <v>1010</v>
       </c>
       <c r="C466" s="4" t="s">
-        <v>1394</v>
+        <v>1384</v>
       </c>
       <c r="D466" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.25">
@@ -11324,10 +11333,10 @@
         <v>1011</v>
       </c>
       <c r="C467" s="4" t="s">
-        <v>1395</v>
+        <v>1381</v>
       </c>
       <c r="D467" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.25">
@@ -11338,10 +11347,10 @@
         <v>1012</v>
       </c>
       <c r="C468" s="4" t="s">
-        <v>1284</v>
+        <v>1426</v>
       </c>
       <c r="D468" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.25">
@@ -11352,10 +11361,10 @@
         <v>1013</v>
       </c>
       <c r="C469" s="4" t="s">
-        <v>1284</v>
+        <v>1426</v>
       </c>
       <c r="D469" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.25">
@@ -11366,10 +11375,10 @@
         <v>1014</v>
       </c>
       <c r="C470" s="4" t="s">
-        <v>1215</v>
+        <v>1286</v>
       </c>
       <c r="D470" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="471" spans="1:4" x14ac:dyDescent="0.25">
@@ -11380,10 +11389,10 @@
         <v>1015</v>
       </c>
       <c r="C471" s="4" t="s">
-        <v>1251</v>
+        <v>1292</v>
       </c>
       <c r="D471" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.25">
@@ -11394,10 +11403,10 @@
         <v>1016</v>
       </c>
       <c r="C472" s="4" t="s">
-        <v>1396</v>
+        <v>1380</v>
       </c>
       <c r="D472" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.25">
@@ -11408,10 +11417,10 @@
         <v>1017</v>
       </c>
       <c r="C473" s="4" t="s">
-        <v>1397</v>
+        <v>1265</v>
       </c>
       <c r="D473" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.25">
@@ -11422,10 +11431,10 @@
         <v>1018</v>
       </c>
       <c r="C474" s="4" t="s">
-        <v>1181</v>
+        <v>1193</v>
       </c>
       <c r="D474" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.25">
@@ -11436,10 +11445,10 @@
         <v>1019</v>
       </c>
       <c r="C475" s="4" t="s">
-        <v>1183</v>
+        <v>1226</v>
       </c>
       <c r="D475" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.25">
@@ -11450,10 +11459,10 @@
         <v>1020</v>
       </c>
       <c r="C476" s="4" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="D476" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.25">
@@ -11464,10 +11473,10 @@
         <v>1021</v>
       </c>
       <c r="C477" s="4" t="s">
-        <v>1398</v>
+        <v>1376</v>
       </c>
       <c r="D477" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.25">
@@ -11478,10 +11487,10 @@
         <v>1022</v>
       </c>
       <c r="C478" s="4" t="s">
-        <v>1399</v>
+        <v>1225</v>
       </c>
       <c r="D478" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.25">
@@ -11492,10 +11501,10 @@
         <v>1023</v>
       </c>
       <c r="C479" s="4" t="s">
-        <v>1400</v>
+        <v>1388</v>
       </c>
       <c r="D479" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="480" spans="1:4" x14ac:dyDescent="0.25">
@@ -11506,10 +11515,10 @@
         <v>1024</v>
       </c>
       <c r="C480" s="4" t="s">
-        <v>1400</v>
+        <v>1388</v>
       </c>
       <c r="D480" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.25">
@@ -11520,10 +11529,10 @@
         <v>1025</v>
       </c>
       <c r="C481" s="4" t="s">
-        <v>1401</v>
+        <v>1391</v>
       </c>
       <c r="D481" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="482" spans="1:4" x14ac:dyDescent="0.25">
@@ -11534,10 +11543,10 @@
         <v>1026</v>
       </c>
       <c r="C482" s="4" t="s">
-        <v>1290</v>
+        <v>1169</v>
       </c>
       <c r="D482" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="483" spans="1:4" x14ac:dyDescent="0.25">
@@ -11548,10 +11557,10 @@
         <v>1027</v>
       </c>
       <c r="C483" s="4" t="s">
-        <v>1402</v>
+        <v>1389</v>
       </c>
       <c r="D483" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="484" spans="1:4" x14ac:dyDescent="0.25">
@@ -11562,10 +11571,10 @@
         <v>1028</v>
       </c>
       <c r="C484" s="4" t="s">
-        <v>1403</v>
+        <v>1392</v>
       </c>
       <c r="D484" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="485" spans="1:4" x14ac:dyDescent="0.25">
@@ -11576,10 +11585,10 @@
         <v>1029</v>
       </c>
       <c r="C485" s="4" t="s">
-        <v>1404</v>
+        <v>1393</v>
       </c>
       <c r="D485" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="486" spans="1:4" x14ac:dyDescent="0.25">
@@ -11590,10 +11599,10 @@
         <v>1030</v>
       </c>
       <c r="C486" s="4" t="s">
-        <v>1120</v>
+        <v>1157</v>
       </c>
       <c r="D486" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.25">
@@ -11604,10 +11613,10 @@
         <v>1031</v>
       </c>
       <c r="C487" s="4" t="s">
-        <v>1320</v>
+        <v>1325</v>
       </c>
       <c r="D487" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="488" spans="1:4" x14ac:dyDescent="0.25">
@@ -11618,10 +11627,10 @@
         <v>1032</v>
       </c>
       <c r="C488" s="4" t="s">
-        <v>1405</v>
+        <v>1390</v>
       </c>
       <c r="D488" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.25">
@@ -11632,10 +11641,10 @@
         <v>1033</v>
       </c>
       <c r="C489" s="4" t="s">
-        <v>1255</v>
+        <v>1239</v>
       </c>
       <c r="D489" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="490" spans="1:4" x14ac:dyDescent="0.25">
@@ -11646,10 +11655,10 @@
         <v>1034</v>
       </c>
       <c r="C490" s="4" t="s">
-        <v>1216</v>
+        <v>1248</v>
       </c>
       <c r="D490" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="491" spans="1:4" x14ac:dyDescent="0.25">
@@ -11660,10 +11669,10 @@
         <v>1035</v>
       </c>
       <c r="C491" s="4" t="s">
-        <v>1362</v>
+        <v>1351</v>
       </c>
       <c r="D491" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="492" spans="1:4" x14ac:dyDescent="0.25">
@@ -11674,10 +11683,10 @@
         <v>1036</v>
       </c>
       <c r="C492" s="4" t="s">
-        <v>1277</v>
+        <v>1333</v>
       </c>
       <c r="D492" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="493" spans="1:4" x14ac:dyDescent="0.25">
@@ -11688,10 +11697,10 @@
         <v>1037</v>
       </c>
       <c r="C493" s="4" t="s">
-        <v>1290</v>
+        <v>1169</v>
       </c>
       <c r="D493" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="494" spans="1:4" x14ac:dyDescent="0.25">
@@ -11702,10 +11711,10 @@
         <v>1038</v>
       </c>
       <c r="C494" s="4" t="s">
-        <v>1397</v>
+        <v>1265</v>
       </c>
       <c r="D494" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="495" spans="1:4" x14ac:dyDescent="0.25">
@@ -11716,10 +11725,10 @@
         <v>1039</v>
       </c>
       <c r="C495" s="4" t="s">
-        <v>1406</v>
+        <v>1263</v>
       </c>
       <c r="D495" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.25">
@@ -11730,10 +11739,10 @@
         <v>1040</v>
       </c>
       <c r="C496" s="4" t="s">
-        <v>1407</v>
+        <v>1264</v>
       </c>
       <c r="D496" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.25">
@@ -11744,10 +11753,10 @@
         <v>1041</v>
       </c>
       <c r="C497" s="4" t="s">
-        <v>1408</v>
+        <v>1262</v>
       </c>
       <c r="D497" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.25">
@@ -11758,10 +11767,10 @@
         <v>1042</v>
       </c>
       <c r="C498" s="4" t="s">
-        <v>1259</v>
+        <v>1209</v>
       </c>
       <c r="D498" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.25">
@@ -11772,38 +11781,38 @@
         <v>1043</v>
       </c>
       <c r="C499" s="4" t="s">
-        <v>1409</v>
+        <v>1227</v>
       </c>
       <c r="D499" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="500" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A500" s="4" t="s">
-        <v>1143</v>
+        <v>1128</v>
       </c>
       <c r="B500" s="4" t="s">
-        <v>1161</v>
+        <v>1146</v>
       </c>
       <c r="C500" s="4" t="s">
-        <v>1452</v>
+        <v>1455</v>
       </c>
       <c r="D500" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="501" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A501" s="4" t="s">
-        <v>1145</v>
+        <v>1130</v>
       </c>
       <c r="B501" s="4" t="s">
-        <v>1163</v>
+        <v>1148</v>
       </c>
       <c r="C501" s="4" t="s">
-        <v>1453</v>
+        <v>1456</v>
       </c>
       <c r="D501" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="502" spans="1:4" x14ac:dyDescent="0.25">
@@ -11814,10 +11823,10 @@
         <v>1044</v>
       </c>
       <c r="C502" s="4" t="s">
-        <v>1231</v>
+        <v>1215</v>
       </c>
       <c r="D502" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="503" spans="1:4" x14ac:dyDescent="0.25">
@@ -11828,10 +11837,10 @@
         <v>1045</v>
       </c>
       <c r="C503" s="4" t="s">
-        <v>1256</v>
+        <v>1241</v>
       </c>
       <c r="D503" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.25">
@@ -11842,10 +11851,10 @@
         <v>1046</v>
       </c>
       <c r="C504" s="4" t="s">
-        <v>1256</v>
+        <v>1241</v>
       </c>
       <c r="D504" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.25">
@@ -11856,10 +11865,10 @@
         <v>1047</v>
       </c>
       <c r="C505" s="4" t="s">
-        <v>1256</v>
+        <v>1241</v>
       </c>
       <c r="D505" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="506" spans="1:4" x14ac:dyDescent="0.25">
@@ -11870,10 +11879,10 @@
         <v>1048</v>
       </c>
       <c r="C506" s="4" t="s">
-        <v>1410</v>
+        <v>1234</v>
       </c>
       <c r="D506" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.25">
@@ -11884,10 +11893,10 @@
         <v>1049</v>
       </c>
       <c r="C507" s="4" t="s">
-        <v>1411</v>
+        <v>1394</v>
       </c>
       <c r="D507" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="508" spans="1:4" x14ac:dyDescent="0.25">
@@ -11898,10 +11907,10 @@
         <v>1050</v>
       </c>
       <c r="C508" s="4" t="s">
-        <v>1412</v>
+        <v>1395</v>
       </c>
       <c r="D508" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.25">
@@ -11912,10 +11921,10 @@
         <v>1051</v>
       </c>
       <c r="C509" s="4" t="s">
-        <v>1256</v>
+        <v>1241</v>
       </c>
       <c r="D509" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="510" spans="1:4" x14ac:dyDescent="0.25">
@@ -11926,10 +11935,10 @@
         <v>1052</v>
       </c>
       <c r="C510" s="4" t="s">
-        <v>1355</v>
+        <v>1363</v>
       </c>
       <c r="D510" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="511" spans="1:4" x14ac:dyDescent="0.25">
@@ -11940,10 +11949,10 @@
         <v>1053</v>
       </c>
       <c r="C511" s="4" t="s">
-        <v>1413</v>
+        <v>1396</v>
       </c>
       <c r="D511" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="512" spans="1:4" x14ac:dyDescent="0.25">
@@ -11954,10 +11963,10 @@
         <v>1054</v>
       </c>
       <c r="C512" s="4" t="s">
-        <v>1414</v>
+        <v>1397</v>
       </c>
       <c r="D512" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="513" spans="1:4" x14ac:dyDescent="0.25">
@@ -11968,10 +11977,10 @@
         <v>1055</v>
       </c>
       <c r="C513" s="4" t="s">
-        <v>1315</v>
+        <v>1296</v>
       </c>
       <c r="D513" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.25">
@@ -11982,10 +11991,10 @@
         <v>1056</v>
       </c>
       <c r="C514" s="4" t="s">
-        <v>1415</v>
+        <v>1398</v>
       </c>
       <c r="D514" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="515" spans="1:4" x14ac:dyDescent="0.25">
@@ -11996,10 +12005,10 @@
         <v>1057</v>
       </c>
       <c r="C515" s="4" t="s">
-        <v>1416</v>
+        <v>1399</v>
       </c>
       <c r="D515" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="516" spans="1:4" x14ac:dyDescent="0.25">
@@ -12013,7 +12022,7 @@
         <v>1168</v>
       </c>
       <c r="D516" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="517" spans="1:4" x14ac:dyDescent="0.25">
@@ -12027,7 +12036,7 @@
         <v>1168</v>
       </c>
       <c r="D517" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="518" spans="1:4" x14ac:dyDescent="0.25">
@@ -12038,10 +12047,10 @@
         <v>1060</v>
       </c>
       <c r="C518" s="4" t="s">
-        <v>1417</v>
+        <v>1400</v>
       </c>
       <c r="D518" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="519" spans="1:4" x14ac:dyDescent="0.25">
@@ -12052,10 +12061,10 @@
         <v>1061</v>
       </c>
       <c r="C519" s="4" t="s">
-        <v>1252</v>
+        <v>1196</v>
       </c>
       <c r="D519" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="520" spans="1:4" x14ac:dyDescent="0.25">
@@ -12066,10 +12075,10 @@
         <v>1062</v>
       </c>
       <c r="C520" s="4" t="s">
-        <v>1385</v>
+        <v>1253</v>
       </c>
       <c r="D520" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.25">
@@ -12080,10 +12089,10 @@
         <v>1063</v>
       </c>
       <c r="C521" s="4" t="s">
-        <v>1385</v>
+        <v>1253</v>
       </c>
       <c r="D521" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="522" spans="1:4" x14ac:dyDescent="0.25">
@@ -12094,10 +12103,10 @@
         <v>1064</v>
       </c>
       <c r="C522" s="4" t="s">
-        <v>1418</v>
+        <v>1254</v>
       </c>
       <c r="D522" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.25">
@@ -12108,10 +12117,10 @@
         <v>1065</v>
       </c>
       <c r="C523" s="4" t="s">
-        <v>1418</v>
+        <v>1254</v>
       </c>
       <c r="D523" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="524" spans="1:4" x14ac:dyDescent="0.25">
@@ -12122,10 +12131,10 @@
         <v>1066</v>
       </c>
       <c r="C524" s="4" t="s">
-        <v>1192</v>
+        <v>1170</v>
       </c>
       <c r="D524" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.25">
@@ -12136,10 +12145,10 @@
         <v>1067</v>
       </c>
       <c r="C525" s="4" t="s">
-        <v>1221</v>
+        <v>1189</v>
       </c>
       <c r="D525" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.25">
@@ -12150,10 +12159,10 @@
         <v>1068</v>
       </c>
       <c r="C526" s="4" t="s">
-        <v>1180</v>
+        <v>1192</v>
       </c>
       <c r="D526" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="527" spans="1:4" x14ac:dyDescent="0.25">
@@ -12164,10 +12173,10 @@
         <v>1069</v>
       </c>
       <c r="C527" s="4" t="s">
-        <v>1419</v>
+        <v>1401</v>
       </c>
       <c r="D527" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.25">
@@ -12178,10 +12187,10 @@
         <v>1070</v>
       </c>
       <c r="C528" s="4" t="s">
-        <v>1420</v>
+        <v>1235</v>
       </c>
       <c r="D528" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="529" spans="1:4" x14ac:dyDescent="0.25">
@@ -12192,10 +12201,10 @@
         <v>1071</v>
       </c>
       <c r="C529" s="4" t="s">
-        <v>1421</v>
+        <v>1242</v>
       </c>
       <c r="D529" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="530" spans="1:4" x14ac:dyDescent="0.25">
@@ -12206,10 +12215,10 @@
         <v>1072</v>
       </c>
       <c r="C530" s="4" t="s">
-        <v>1422</v>
+        <v>1402</v>
       </c>
       <c r="D530" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="531" spans="1:4" x14ac:dyDescent="0.25">
@@ -12220,10 +12229,10 @@
         <v>1073</v>
       </c>
       <c r="C531" s="4" t="s">
-        <v>1191</v>
+        <v>1172</v>
       </c>
       <c r="D531" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.25">
@@ -12234,10 +12243,10 @@
         <v>1074</v>
       </c>
       <c r="C532" s="4" t="s">
-        <v>1359</v>
+        <v>1236</v>
       </c>
       <c r="D532" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="533" spans="1:4" x14ac:dyDescent="0.25">
@@ -12248,10 +12257,10 @@
         <v>1075</v>
       </c>
       <c r="C533" s="4" t="s">
-        <v>1171</v>
+        <v>1200</v>
       </c>
       <c r="D533" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="534" spans="1:4" x14ac:dyDescent="0.25">
@@ -12262,10 +12271,10 @@
         <v>1076</v>
       </c>
       <c r="C534" s="4" t="s">
-        <v>1423</v>
+        <v>1403</v>
       </c>
       <c r="D534" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="535" spans="1:4" x14ac:dyDescent="0.25">
@@ -12276,10 +12285,10 @@
         <v>1077</v>
       </c>
       <c r="C535" s="4" t="s">
-        <v>1423</v>
+        <v>1403</v>
       </c>
       <c r="D535" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="536" spans="1:4" x14ac:dyDescent="0.25">
@@ -12290,10 +12299,10 @@
         <v>1078</v>
       </c>
       <c r="C536" s="4" t="s">
-        <v>1424</v>
+        <v>1404</v>
       </c>
       <c r="D536" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="537" spans="1:4" x14ac:dyDescent="0.25">
@@ -12304,10 +12313,10 @@
         <v>1079</v>
       </c>
       <c r="C537" s="4" t="s">
-        <v>1316</v>
+        <v>1352</v>
       </c>
       <c r="D537" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="538" spans="1:4" x14ac:dyDescent="0.25">
@@ -12318,10 +12327,10 @@
         <v>1080</v>
       </c>
       <c r="C538" s="4" t="s">
-        <v>1425</v>
+        <v>1405</v>
       </c>
       <c r="D538" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.25">
@@ -12332,10 +12341,10 @@
         <v>1081</v>
       </c>
       <c r="C539" s="4" t="s">
-        <v>1426</v>
+        <v>1406</v>
       </c>
       <c r="D539" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="540" spans="1:4" x14ac:dyDescent="0.25">
@@ -12346,10 +12355,10 @@
         <v>1082</v>
       </c>
       <c r="C540" s="4" t="s">
-        <v>1427</v>
+        <v>1407</v>
       </c>
       <c r="D540" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.25">
@@ -12360,10 +12369,10 @@
         <v>1083</v>
       </c>
       <c r="C541" s="4" t="s">
-        <v>1359</v>
+        <v>1236</v>
       </c>
       <c r="D541" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="542" spans="1:4" x14ac:dyDescent="0.25">
@@ -12374,10 +12383,10 @@
         <v>1084</v>
       </c>
       <c r="C542" s="4" t="s">
-        <v>1340</v>
+        <v>1237</v>
       </c>
       <c r="D542" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="543" spans="1:4" x14ac:dyDescent="0.25">
@@ -12388,10 +12397,10 @@
         <v>1085</v>
       </c>
       <c r="C543" s="4" t="s">
-        <v>1428</v>
+        <v>1408</v>
       </c>
       <c r="D543" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="544" spans="1:4" x14ac:dyDescent="0.25">
@@ -12402,10 +12411,10 @@
         <v>1086</v>
       </c>
       <c r="C544" s="4" t="s">
-        <v>1429</v>
+        <v>1409</v>
       </c>
       <c r="D544" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.25">
@@ -12416,10 +12425,10 @@
         <v>1087</v>
       </c>
       <c r="C545" s="4" t="s">
-        <v>1430</v>
+        <v>1410</v>
       </c>
       <c r="D545" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="546" spans="1:4" x14ac:dyDescent="0.25">
@@ -12430,10 +12439,10 @@
         <v>1088</v>
       </c>
       <c r="C546" s="4" t="s">
-        <v>1358</v>
+        <v>1220</v>
       </c>
       <c r="D546" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="547" spans="1:4" x14ac:dyDescent="0.25">
@@ -12444,10 +12453,10 @@
         <v>1089</v>
       </c>
       <c r="C547" s="4" t="s">
-        <v>1431</v>
+        <v>1411</v>
       </c>
       <c r="D547" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="548" spans="1:4" x14ac:dyDescent="0.25">
@@ -12458,10 +12467,10 @@
         <v>1090</v>
       </c>
       <c r="C548" s="4" t="s">
-        <v>1381</v>
+        <v>1374</v>
       </c>
       <c r="D548" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="549" spans="1:4" x14ac:dyDescent="0.25">
@@ -12472,10 +12481,10 @@
         <v>1091</v>
       </c>
       <c r="C549" s="4" t="s">
-        <v>1432</v>
+        <v>1412</v>
       </c>
       <c r="D549" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.25">
@@ -12486,10 +12495,10 @@
         <v>1092</v>
       </c>
       <c r="C550" s="4" t="s">
-        <v>1186</v>
+        <v>1245</v>
       </c>
       <c r="D550" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="551" spans="1:4" x14ac:dyDescent="0.25">
@@ -12500,10 +12509,10 @@
         <v>1093</v>
       </c>
       <c r="C551" s="4" t="s">
-        <v>1433</v>
+        <v>1413</v>
       </c>
       <c r="D551" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="552" spans="1:4" x14ac:dyDescent="0.25">
@@ -12514,10 +12523,10 @@
         <v>1094</v>
       </c>
       <c r="C552" s="4" t="s">
-        <v>1434</v>
+        <v>1414</v>
       </c>
       <c r="D552" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="553" spans="1:4" x14ac:dyDescent="0.25">
@@ -12528,10 +12537,10 @@
         <v>1095</v>
       </c>
       <c r="C553" s="4" t="s">
-        <v>1233</v>
+        <v>1315</v>
       </c>
       <c r="D553" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="554" spans="1:4" x14ac:dyDescent="0.25">
@@ -12542,10 +12551,10 @@
         <v>1096</v>
       </c>
       <c r="C554" s="4" t="s">
-        <v>1435</v>
+        <v>1415</v>
       </c>
       <c r="D554" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="555" spans="1:4" x14ac:dyDescent="0.25">
@@ -12556,10 +12565,10 @@
         <v>1097</v>
       </c>
       <c r="C555" s="4" t="s">
-        <v>1436</v>
+        <v>1416</v>
       </c>
       <c r="D555" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="556" spans="1:4" x14ac:dyDescent="0.25">
@@ -12570,10 +12579,10 @@
         <v>1098</v>
       </c>
       <c r="C556" s="4" t="s">
-        <v>1437</v>
+        <v>1417</v>
       </c>
       <c r="D556" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="557" spans="1:4" x14ac:dyDescent="0.25">
@@ -12584,10 +12593,10 @@
         <v>1099</v>
       </c>
       <c r="C557" s="4" t="s">
-        <v>1438</v>
+        <v>1418</v>
       </c>
       <c r="D557" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="558" spans="1:4" x14ac:dyDescent="0.25">
@@ -12598,10 +12607,10 @@
         <v>1100</v>
       </c>
       <c r="C558" s="4" t="s">
-        <v>1439</v>
+        <v>1419</v>
       </c>
       <c r="D558" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.25">
@@ -12612,10 +12621,10 @@
         <v>1101</v>
       </c>
       <c r="C559" s="4" t="s">
-        <v>1440</v>
+        <v>1420</v>
       </c>
       <c r="D559" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="560" spans="1:4" x14ac:dyDescent="0.25">
@@ -12626,10 +12635,10 @@
         <v>1102</v>
       </c>
       <c r="C560" s="4" t="s">
-        <v>1441</v>
+        <v>1421</v>
       </c>
       <c r="D560" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="561" spans="1:4" x14ac:dyDescent="0.25">
@@ -12640,10 +12649,10 @@
         <v>1103</v>
       </c>
       <c r="C561" s="4" t="s">
-        <v>1266</v>
+        <v>1301</v>
       </c>
       <c r="D561" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="562" spans="1:4" x14ac:dyDescent="0.25">
@@ -12654,10 +12663,10 @@
         <v>1104</v>
       </c>
       <c r="C562" s="4" t="s">
-        <v>1255</v>
+        <v>1239</v>
       </c>
       <c r="D562" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="563" spans="1:4" x14ac:dyDescent="0.25">
@@ -12668,10 +12677,10 @@
         <v>1105</v>
       </c>
       <c r="C563" s="4" t="s">
-        <v>1442</v>
+        <v>1176</v>
       </c>
       <c r="D563" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="564" spans="1:4" x14ac:dyDescent="0.25">
@@ -12682,10 +12691,10 @@
         <v>1106</v>
       </c>
       <c r="C564" s="4" t="s">
-        <v>1442</v>
+        <v>1176</v>
       </c>
       <c r="D564" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="565" spans="1:4" x14ac:dyDescent="0.25">
@@ -12696,10 +12705,10 @@
         <v>1107</v>
       </c>
       <c r="C565" s="4" t="s">
-        <v>1443</v>
+        <v>1266</v>
       </c>
       <c r="D565" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="566" spans="1:4" x14ac:dyDescent="0.25">
@@ -12710,10 +12719,10 @@
         <v>1108</v>
       </c>
       <c r="C566" s="4" t="s">
-        <v>1381</v>
+        <v>1374</v>
       </c>
       <c r="D566" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="567" spans="1:4" x14ac:dyDescent="0.25">
@@ -12724,10 +12733,10 @@
         <v>1109</v>
       </c>
       <c r="C567" s="4" t="s">
-        <v>1443</v>
+        <v>1266</v>
       </c>
       <c r="D567" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.25">
@@ -12738,10 +12747,10 @@
         <v>1110</v>
       </c>
       <c r="C568" s="4" t="s">
-        <v>1254</v>
+        <v>1238</v>
       </c>
       <c r="D568" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="569" spans="1:4" x14ac:dyDescent="0.25">
@@ -12752,10 +12761,10 @@
         <v>1111</v>
       </c>
       <c r="C569" s="4" t="s">
-        <v>1254</v>
+        <v>1238</v>
       </c>
       <c r="D569" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="570" spans="1:4" x14ac:dyDescent="0.25">
@@ -12766,10 +12775,10 @@
         <v>1112</v>
       </c>
       <c r="C570" s="4" t="s">
-        <v>1254</v>
+        <v>1238</v>
       </c>
       <c r="D570" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="571" spans="1:4" x14ac:dyDescent="0.25">
@@ -12780,14 +12789,25 @@
         <v>1113</v>
       </c>
       <c r="C571" s="4" t="s">
-        <v>1444</v>
+        <v>1422</v>
       </c>
       <c r="D571" s="4" t="s">
-        <v>1131</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="572" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C572" s="2"/>
+      <c r="A572" s="4" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B572" s="4" t="s">
+        <v>1424</v>
+      </c>
+      <c r="C572" s="4" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D572" s="4" t="s">
+        <v>1116</v>
+      </c>
     </row>
     <row r="573" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C573" s="2"/>
